--- a/data/base_gestor_locator.xlsx
+++ b/data/base_gestor_locator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA1365B-4EEF-4812-A6C5-F3BEA075A8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94DF8F6-0220-47BD-A41B-A6088EAFF8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AF7731-6CD9-46EC-B877-B9E0C87BB669}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$X$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$X$347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="44">
   <si>
     <t>Data</t>
   </si>
@@ -549,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAFC8DE-6478-4031-89A9-FB95FCFA4EDA}">
-  <dimension ref="A1:X446"/>
+  <dimension ref="A1:X437"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -25795,10 +25795,10 @@
     </row>
     <row r="348" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B348">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C348">
         <v>81</v>
@@ -25816,52 +25816,52 @@
         <v>50</v>
       </c>
       <c r="H348">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I348">
-        <v>4818</v>
+        <v>20711</v>
       </c>
       <c r="J348">
-        <v>64</v>
+        <v>270</v>
       </c>
       <c r="K348">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="L348">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M348">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="N348">
         <v>1</v>
       </c>
       <c r="O348" s="2">
-        <v>8.6805555555555551E-4</v>
+        <v>8.7962962962962962E-4</v>
       </c>
       <c r="P348" s="2">
-        <v>2.5347222222222221E-3</v>
+        <v>1.5162037037037036E-3</v>
       </c>
       <c r="Q348" s="3">
-        <v>1.3299999999999999E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R348" s="3">
-        <v>0.15629999999999999</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="S348" s="4">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="T348">
-        <v>1</v>
-      </c>
-      <c r="U348" s="3">
-        <v>0.1429</v>
+        <v>-37</v>
+      </c>
+      <c r="U348" t="s">
+        <v>25</v>
       </c>
       <c r="V348" s="3">
-        <v>0.71430000000000005</v>
+        <v>0.8679</v>
       </c>
       <c r="W348">
-        <v>14.513999999999999</v>
+        <v>56.67</v>
       </c>
       <c r="X348" t="s">
         <v>41</v>
@@ -25869,10 +25869,10 @@
     </row>
     <row r="349" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B349">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C349">
         <v>81</v>
@@ -25890,52 +25890,52 @@
         <v>50</v>
       </c>
       <c r="H349">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I349">
-        <v>5514</v>
+        <v>16842</v>
       </c>
       <c r="J349">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="K349">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L349">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M349">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="N349">
         <v>1</v>
       </c>
       <c r="O349" s="2">
-        <v>7.407407407407407E-4</v>
+        <v>1.3194444444444445E-3</v>
       </c>
       <c r="P349" s="2">
-        <v>1.736111111111111E-3</v>
+        <v>1.5393518518518519E-3</v>
       </c>
       <c r="Q349" s="3">
-        <v>1.5599999999999999E-2</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="R349" s="3">
-        <v>0.1512</v>
-      </c>
-      <c r="S349" s="3">
-        <v>0.30769999999999997</v>
+        <v>0.1905</v>
+      </c>
+      <c r="S349" s="4">
+        <v>1</v>
       </c>
       <c r="T349">
-        <v>0</v>
-      </c>
-      <c r="U349" s="4">
-        <v>0</v>
+        <v>-21</v>
+      </c>
+      <c r="U349" t="s">
+        <v>25</v>
       </c>
       <c r="V349" s="3">
         <v>1</v>
       </c>
       <c r="W349">
-        <v>17.928000000000001</v>
+        <v>14.574</v>
       </c>
       <c r="X349" t="s">
         <v>41</v>
@@ -25943,10 +25943,10 @@
     </row>
     <row r="350" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B350">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C350">
         <v>81</v>
@@ -25961,55 +25961,55 @@
         <v>43</v>
       </c>
       <c r="G350">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H350">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I350">
-        <v>2058</v>
+        <v>20557</v>
       </c>
       <c r="J350">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="K350">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L350">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M350">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="N350">
         <v>1</v>
       </c>
       <c r="O350" s="2">
-        <v>6.018518518518519E-4</v>
+        <v>1.7592592592592592E-3</v>
       </c>
       <c r="P350" s="2">
-        <v>2.9513888888888888E-3</v>
+        <v>1.4699074074074074E-3</v>
       </c>
       <c r="Q350" s="3">
-        <v>1.9E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="R350" s="3">
-        <v>0.23080000000000001</v>
-      </c>
-      <c r="S350" s="3">
-        <v>0.22220000000000001</v>
+        <v>0.1852</v>
+      </c>
+      <c r="S350" s="4">
+        <v>1</v>
       </c>
       <c r="T350">
-        <v>3</v>
-      </c>
-      <c r="U350" s="3">
-        <v>0.42859999999999998</v>
+        <v>-19</v>
+      </c>
+      <c r="U350" t="s">
+        <v>25</v>
       </c>
       <c r="V350" s="3">
-        <v>0.71430000000000005</v>
+        <v>0.88239999999999996</v>
       </c>
       <c r="W350">
-        <v>7.5060000000000002</v>
+        <v>11.885999999999999</v>
       </c>
       <c r="X350" t="s">
         <v>41</v>
@@ -26017,10 +26017,10 @@
     </row>
     <row r="351" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B351">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C351">
         <v>81</v>
@@ -26035,55 +26035,55 @@
         <v>43</v>
       </c>
       <c r="G351">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H351">
+        <v>0</v>
+      </c>
+      <c r="I351">
+        <v>277</v>
+      </c>
+      <c r="J351">
         <v>2</v>
       </c>
-      <c r="I351">
-        <v>5147</v>
-      </c>
-      <c r="J351">
-        <v>64</v>
-      </c>
       <c r="K351">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L351">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M351">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O351" s="2">
-        <v>9.2592592592592596E-4</v>
-      </c>
-      <c r="P351" s="2">
-        <v>3.9930555555555552E-3</v>
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="P351" t="s">
+        <v>24</v>
       </c>
       <c r="Q351" s="3">
-        <v>1.24E-2</v>
-      </c>
-      <c r="R351" s="3">
-        <v>0.15629999999999999</v>
-      </c>
-      <c r="S351" s="4">
-        <v>0.2</v>
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R351" s="4">
+        <v>0</v>
+      </c>
+      <c r="S351" t="s">
+        <v>25</v>
       </c>
       <c r="T351">
-        <v>5</v>
-      </c>
-      <c r="U351" s="3">
-        <v>0.625</v>
+        <v>0</v>
+      </c>
+      <c r="U351" t="s">
+        <v>25</v>
       </c>
       <c r="V351" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W351">
-        <v>13.476000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="X351" t="s">
         <v>41</v>
@@ -26091,10 +26091,10 @@
     </row>
     <row r="352" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B352">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C352">
         <v>81</v>
@@ -26109,55 +26109,55 @@
         <v>43</v>
       </c>
       <c r="G352">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="H352">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I352">
-        <v>10780</v>
+        <v>1171</v>
       </c>
       <c r="J352">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="K352">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L352">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M352">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N352">
         <v>0</v>
       </c>
       <c r="O352" s="2">
-        <v>1.4467592592592592E-3</v>
-      </c>
-      <c r="P352" t="s">
-        <v>24</v>
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="P352" s="2">
+        <v>5.6712962962962967E-4</v>
       </c>
       <c r="Q352" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R352" s="4">
-        <v>0</v>
-      </c>
-      <c r="S352" t="s">
-        <v>25</v>
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R352" s="3">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="S352" s="4">
+        <v>1</v>
       </c>
       <c r="T352">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U352" t="s">
         <v>25</v>
       </c>
-      <c r="V352" t="s">
-        <v>25</v>
+      <c r="V352" s="3">
+        <v>1</v>
       </c>
       <c r="W352">
-        <v>21.3</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="X352" t="s">
         <v>41</v>
@@ -26165,10 +26165,10 @@
     </row>
     <row r="353" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B353">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C353">
         <v>81</v>
@@ -26186,52 +26186,52 @@
         <v>50</v>
       </c>
       <c r="H353">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I353">
-        <v>12161</v>
+        <v>20275</v>
       </c>
       <c r="J353">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="K353">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L353">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="M353">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N353">
         <v>0</v>
       </c>
       <c r="O353" s="2">
-        <v>9.2592592592592596E-4</v>
+        <v>9.7222222222222219E-4</v>
       </c>
       <c r="P353" s="2">
-        <v>1.238425925925926E-3</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="Q353" s="3">
-        <v>1.24E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="R353" s="3">
-        <v>0.27150000000000002</v>
-      </c>
-      <c r="S353" s="3">
-        <v>0.39019999999999999</v>
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="S353" s="4">
+        <v>1</v>
       </c>
       <c r="T353">
-        <v>2</v>
-      </c>
-      <c r="U353" s="4">
-        <v>0.08</v>
+        <v>-25</v>
+      </c>
+      <c r="U353" t="s">
+        <v>25</v>
       </c>
       <c r="V353" s="3">
-        <v>0.84</v>
+        <v>0.87880000000000003</v>
       </c>
       <c r="W353">
-        <v>34.11</v>
+        <v>34.314</v>
       </c>
       <c r="X353" t="s">
         <v>41</v>
@@ -26239,10 +26239,10 @@
     </row>
     <row r="354" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B354">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C354">
         <v>84</v>
@@ -26257,52 +26257,52 @@
         <v>43</v>
       </c>
       <c r="G354">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H354">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I354">
-        <v>2</v>
+        <v>4199</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="K354">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L354">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M354">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N354">
         <v>0</v>
       </c>
       <c r="O354" s="2">
-        <v>2.3148148148148147E-5</v>
-      </c>
-      <c r="P354" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q354" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="R354" s="4">
-        <v>0</v>
-      </c>
-      <c r="S354" t="s">
-        <v>25</v>
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="P354" s="2">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q354" s="3">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="R354" s="3">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="S354" s="4">
+        <v>1</v>
       </c>
       <c r="T354">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="U354" t="s">
         <v>25</v>
       </c>
       <c r="W354">
-        <v>0.03</v>
+        <v>16.956</v>
       </c>
       <c r="X354" t="s">
         <v>41</v>
@@ -26310,10 +26310,10 @@
     </row>
     <row r="355" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B355">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C355">
         <v>81</v>
@@ -26328,52 +26328,55 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H355">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I355">
-        <v>1</v>
+        <v>14008</v>
       </c>
       <c r="J355">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K355">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L355">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M355">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N355">
         <v>0</v>
       </c>
-      <c r="O355" t="s">
-        <v>24</v>
-      </c>
-      <c r="P355" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q355" s="4">
-        <v>0</v>
-      </c>
-      <c r="R355" t="s">
-        <v>25</v>
-      </c>
-      <c r="S355" t="s">
-        <v>25</v>
+      <c r="O355" s="2">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="P355" s="2">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="Q355" s="3">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="R355" s="3">
+        <v>0.23119999999999999</v>
+      </c>
+      <c r="S355" s="4">
+        <v>1</v>
       </c>
       <c r="T355">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="U355" t="s">
         <v>25</v>
       </c>
-      <c r="V355" t="s">
-        <v>25</v>
+      <c r="V355" s="3">
+        <v>0.6774</v>
+      </c>
+      <c r="W355">
+        <v>10.5</v>
       </c>
       <c r="X355" t="s">
         <v>41</v>
@@ -26381,10 +26384,10 @@
     </row>
     <row r="356" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B356">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C356">
         <v>84</v>
@@ -26399,49 +26402,52 @@
         <v>43</v>
       </c>
       <c r="G356">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I356">
-        <v>1</v>
+        <v>9091</v>
       </c>
       <c r="J356">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="K356">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="L356">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M356">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N356">
         <v>0</v>
       </c>
-      <c r="O356" t="s">
-        <v>24</v>
-      </c>
-      <c r="P356" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q356" s="4">
-        <v>0</v>
-      </c>
-      <c r="R356" t="s">
-        <v>25</v>
-      </c>
-      <c r="S356" t="s">
-        <v>25</v>
+      <c r="O356" s="2">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="P356" s="2">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="Q356" s="3">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="R356" s="3">
+        <v>0.29120000000000001</v>
+      </c>
+      <c r="S356" s="4">
+        <v>1</v>
       </c>
       <c r="T356">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="U356" t="s">
         <v>25</v>
+      </c>
+      <c r="W356">
+        <v>7.8479999999999999</v>
       </c>
       <c r="X356" t="s">
         <v>41</v>
@@ -26452,7 +26458,7 @@
         <v>46181</v>
       </c>
       <c r="B357">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C357">
         <v>81</v>
@@ -26467,55 +26473,52 @@
         <v>43</v>
       </c>
       <c r="G357">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H357">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I357">
-        <v>20711</v>
+        <v>361</v>
       </c>
       <c r="J357">
-        <v>270</v>
+        <v>3</v>
       </c>
       <c r="K357">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="L357">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M357">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O357" s="2">
-        <v>8.7962962962962962E-4</v>
+        <v>1.3773148148148147E-3</v>
       </c>
       <c r="P357" s="2">
-        <v>1.5162037037037036E-3</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q357" s="3">
-        <v>1.2999999999999999E-2</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="R357" s="3">
-        <v>0.26669999999999999</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="S357" s="4">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="T357">
-        <v>17</v>
-      </c>
-      <c r="U357" s="3">
-        <v>0.31480000000000002</v>
+        <v>-1</v>
+      </c>
+      <c r="U357" t="s">
+        <v>25</v>
       </c>
       <c r="V357" s="3">
-        <v>0.8679</v>
-      </c>
-      <c r="W357">
-        <v>56.67</v>
+        <v>0</v>
       </c>
       <c r="X357" t="s">
         <v>41</v>
@@ -26526,70 +26529,64 @@
         <v>46181</v>
       </c>
       <c r="B358">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C358">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D358">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E358" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F358" t="s">
         <v>43</v>
       </c>
       <c r="G358">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H358">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I358">
-        <v>16842</v>
+        <v>3492</v>
       </c>
       <c r="J358">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="K358">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L358">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="M358">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N358">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O358" s="2">
-        <v>1.3194444444444445E-3</v>
+        <v>4.2824074074074075E-4</v>
       </c>
       <c r="P358" s="2">
-        <v>1.5393518518518519E-3</v>
+        <v>2.1990740740740742E-3</v>
       </c>
       <c r="Q358" s="3">
-        <v>8.6999999999999994E-3</v>
+        <v>2.69E-2</v>
       </c>
       <c r="R358" s="3">
-        <v>0.2041</v>
-      </c>
-      <c r="S358" s="3">
-        <v>0.26669999999999999</v>
+        <v>0.34039999999999998</v>
+      </c>
+      <c r="S358" s="4">
+        <v>1</v>
       </c>
       <c r="T358">
-        <v>1</v>
-      </c>
-      <c r="U358" s="3">
-        <v>4.5499999999999999E-2</v>
-      </c>
-      <c r="V358" s="3">
-        <v>1</v>
-      </c>
-      <c r="W358">
-        <v>14.574</v>
+        <v>-4</v>
+      </c>
+      <c r="U358" t="s">
+        <v>25</v>
       </c>
       <c r="X358" t="s">
         <v>41</v>
@@ -26597,10 +26594,10 @@
     </row>
     <row r="359" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B359">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C359">
         <v>81</v>
@@ -26615,55 +26612,52 @@
         <v>43</v>
       </c>
       <c r="G359">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H359">
         <v>4</v>
       </c>
       <c r="I359">
-        <v>20557</v>
+        <v>18719</v>
       </c>
       <c r="J359">
-        <v>135</v>
+        <v>232</v>
       </c>
       <c r="K359">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L359">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="M359">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N359">
         <v>1</v>
       </c>
       <c r="O359" s="2">
-        <v>1.7592592592592592E-3</v>
+        <v>8.9120370370370373E-4</v>
       </c>
       <c r="P359" s="2">
-        <v>1.4699074074074074E-3</v>
+        <v>1.2037037037037038E-3</v>
       </c>
       <c r="Q359" s="3">
-        <v>6.6E-3</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R359" s="3">
-        <v>0.2074</v>
-      </c>
-      <c r="S359" s="3">
-        <v>0.32140000000000002</v>
+        <v>0.15090000000000001</v>
+      </c>
+      <c r="S359" s="4">
+        <v>1</v>
       </c>
       <c r="T359">
-        <v>0</v>
-      </c>
-      <c r="U359" s="4">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="U359" t="s">
+        <v>25</v>
       </c>
       <c r="V359" s="3">
-        <v>0.88239999999999996</v>
-      </c>
-      <c r="W359">
-        <v>11.885999999999999</v>
+        <v>0.95240000000000002</v>
       </c>
       <c r="X359" t="s">
         <v>41</v>
@@ -26671,10 +26665,10 @@
     </row>
     <row r="360" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B360">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C360">
         <v>81</v>
@@ -26689,55 +26683,52 @@
         <v>43</v>
       </c>
       <c r="G360">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I360">
-        <v>277</v>
+        <v>20163</v>
       </c>
       <c r="J360">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="K360">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L360">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M360">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N360">
         <v>0</v>
       </c>
       <c r="O360" s="2">
-        <v>1.5972222222222223E-3</v>
-      </c>
-      <c r="P360" t="s">
-        <v>24</v>
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="P360" s="2">
+        <v>9.3749999999999997E-4</v>
       </c>
       <c r="Q360" s="3">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="R360" s="4">
-        <v>0</v>
-      </c>
-      <c r="S360" t="s">
-        <v>25</v>
+        <v>1.24E-2</v>
+      </c>
+      <c r="R360" s="3">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="S360" s="4">
+        <v>1</v>
       </c>
       <c r="T360">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="U360" t="s">
         <v>25</v>
       </c>
       <c r="V360" s="3">
-        <v>1</v>
-      </c>
-      <c r="W360">
-        <v>0.03</v>
+        <v>0.85289999999999999</v>
       </c>
       <c r="X360" t="s">
         <v>41</v>
@@ -26745,10 +26736,10 @@
     </row>
     <row r="361" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B361">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C361">
         <v>81</v>
@@ -26763,55 +26754,52 @@
         <v>43</v>
       </c>
       <c r="G361">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H361">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I361">
-        <v>1171</v>
+        <v>12067</v>
       </c>
       <c r="J361">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="K361">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L361">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M361">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N361">
         <v>0</v>
       </c>
       <c r="O361" s="2">
-        <v>1.5046296296296296E-3</v>
+        <v>1.1226851851851851E-3</v>
       </c>
       <c r="P361" s="2">
-        <v>5.6712962962962967E-4</v>
-      </c>
-      <c r="Q361" s="3">
-        <v>7.7000000000000002E-3</v>
+        <v>1.7824074074074075E-3</v>
+      </c>
+      <c r="Q361" s="4">
+        <v>0.01</v>
       </c>
       <c r="R361" s="3">
-        <v>0.22220000000000001</v>
+        <v>0.14050000000000001</v>
       </c>
       <c r="S361" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T361">
-        <v>0</v>
-      </c>
-      <c r="U361" s="4">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="U361" t="s">
+        <v>25</v>
       </c>
       <c r="V361" s="3">
         <v>1</v>
-      </c>
-      <c r="W361">
-        <v>0.79800000000000004</v>
       </c>
       <c r="X361" t="s">
         <v>41</v>
@@ -26819,73 +26807,67 @@
     </row>
     <row r="362" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B362">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C362">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D362">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E362" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F362" t="s">
         <v>43</v>
       </c>
       <c r="G362">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H362">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I362">
-        <v>20275</v>
+        <v>8477</v>
       </c>
       <c r="J362">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="K362">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="L362">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="M362">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N362">
         <v>0</v>
       </c>
       <c r="O362" s="2">
-        <v>9.7222222222222219E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="P362" s="2">
-        <v>1.736111111111111E-3</v>
+        <v>6.3657407407407413E-4</v>
       </c>
       <c r="Q362" s="3">
-        <v>1.1900000000000001E-2</v>
+        <v>3.7199999999999997E-2</v>
       </c>
       <c r="R362" s="3">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="S362" s="3">
-        <v>0.31909999999999999</v>
+        <v>0.254</v>
+      </c>
+      <c r="S362" s="4">
+        <v>1</v>
       </c>
       <c r="T362">
-        <v>7</v>
-      </c>
-      <c r="U362" s="3">
-        <v>0.21879999999999999</v>
-      </c>
-      <c r="V362" s="3">
-        <v>0.87880000000000003</v>
-      </c>
-      <c r="W362">
-        <v>34.314</v>
+        <v>-58</v>
+      </c>
+      <c r="U362" t="s">
+        <v>25</v>
       </c>
       <c r="X362" t="s">
         <v>41</v>
@@ -26893,70 +26875,70 @@
     </row>
     <row r="363" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B363">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C363">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D363">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E363" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F363" t="s">
         <v>43</v>
       </c>
       <c r="G363">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H363">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I363">
-        <v>4199</v>
+        <v>9021</v>
       </c>
       <c r="J363">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="K363">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="L363">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M363">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N363">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O363" s="2">
-        <v>2.8935185185185184E-4</v>
+        <v>1.1574074074074073E-3</v>
       </c>
       <c r="P363" s="2">
-        <v>5.6712962962962967E-4</v>
+        <v>1.4004629629629629E-3</v>
       </c>
       <c r="Q363" s="3">
-        <v>3.8800000000000001E-2</v>
-      </c>
-      <c r="R363" s="3">
-        <v>0.36199999999999999</v>
-      </c>
-      <c r="S363" s="3">
-        <v>0.38979999999999998</v>
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="R363" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S363" s="4">
+        <v>1</v>
       </c>
       <c r="T363">
-        <v>3</v>
-      </c>
-      <c r="U363" s="3">
-        <v>8.3299999999999999E-2</v>
-      </c>
-      <c r="W363">
-        <v>16.956</v>
+        <v>-10</v>
+      </c>
+      <c r="U363" t="s">
+        <v>25</v>
+      </c>
+      <c r="V363" s="3">
+        <v>1</v>
       </c>
       <c r="X363" t="s">
         <v>41</v>
@@ -26964,73 +26946,67 @@
     </row>
     <row r="364" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B364">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C364">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D364">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E364" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F364" t="s">
         <v>43</v>
       </c>
       <c r="G364">
+        <v>25</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>6627</v>
+      </c>
+      <c r="J364">
+        <v>232</v>
+      </c>
+      <c r="K364">
         <v>50</v>
       </c>
-      <c r="H364">
+      <c r="L364">
+        <v>50</v>
+      </c>
+      <c r="M364">
         <v>4</v>
       </c>
-      <c r="I364">
-        <v>14008</v>
-      </c>
-      <c r="J364">
-        <v>186</v>
-      </c>
-      <c r="K364">
-        <v>237</v>
-      </c>
-      <c r="L364">
-        <v>17</v>
-      </c>
-      <c r="M364">
-        <v>21</v>
-      </c>
       <c r="N364">
         <v>0</v>
       </c>
       <c r="O364" s="2">
-        <v>8.564814814814815E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="P364" s="2">
-        <v>1.4583333333333334E-3</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q364" s="3">
-        <v>1.3299999999999999E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="R364" s="3">
-        <v>1.274</v>
-      </c>
-      <c r="S364" s="3">
-        <v>7.17E-2</v>
+        <v>0.2155</v>
+      </c>
+      <c r="S364" s="4">
+        <v>1</v>
       </c>
       <c r="T364">
-        <v>199</v>
-      </c>
-      <c r="U364" s="3">
-        <v>0.90449999999999997</v>
-      </c>
-      <c r="V364" s="3">
-        <v>0.6774</v>
-      </c>
-      <c r="W364">
-        <v>10.5</v>
+        <v>-4</v>
+      </c>
+      <c r="U364" t="s">
+        <v>25</v>
       </c>
       <c r="X364" t="s">
         <v>41</v>
@@ -27038,70 +27014,70 @@
     </row>
     <row r="365" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B365">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C365">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D365">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E365" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F365" t="s">
         <v>43</v>
       </c>
       <c r="G365">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H365">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I365">
-        <v>9091</v>
+        <v>14219</v>
       </c>
       <c r="J365">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="K365">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="L365">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M365">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="N365">
         <v>0</v>
       </c>
       <c r="O365" s="2">
-        <v>3.5879629629629629E-4</v>
+        <v>8.4490740740740739E-4</v>
       </c>
       <c r="P365" s="2">
-        <v>9.9537037037037042E-4</v>
+        <v>1.736111111111111E-3</v>
       </c>
       <c r="Q365" s="3">
-        <v>3.1300000000000001E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="R365" s="3">
-        <v>0.52629999999999999</v>
-      </c>
-      <c r="S365" s="3">
-        <v>0.33329999999999999</v>
+        <v>0.1429</v>
+      </c>
+      <c r="S365" s="4">
+        <v>1</v>
       </c>
       <c r="T365">
-        <v>67</v>
-      </c>
-      <c r="U365" s="4">
-        <v>0.67</v>
-      </c>
-      <c r="W365">
-        <v>7.8479999999999999</v>
+        <v>-14</v>
+      </c>
+      <c r="U365" t="s">
+        <v>25</v>
+      </c>
+      <c r="V365" s="3">
+        <v>1</v>
       </c>
       <c r="X365" t="s">
         <v>41</v>
@@ -27109,70 +27085,67 @@
     </row>
     <row r="366" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B366">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C366">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D366">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E366" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F366" t="s">
         <v>43</v>
       </c>
       <c r="G366">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H366">
         <v>1</v>
       </c>
       <c r="I366">
-        <v>361</v>
+        <v>4319</v>
       </c>
       <c r="J366">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="K366">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L366">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M366">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N366">
         <v>0</v>
       </c>
       <c r="O366" s="2">
-        <v>1.3773148148148147E-3</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="P366" s="2">
-        <v>7.6388888888888893E-4</v>
+        <v>5.3240740740740744E-4</v>
       </c>
       <c r="Q366" s="3">
-        <v>8.3000000000000001E-3</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="R366" s="3">
-        <v>0.33329999999999999</v>
+        <v>0.24390000000000001</v>
       </c>
       <c r="S366" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T366">
-        <v>0</v>
-      </c>
-      <c r="U366" s="4">
-        <v>0</v>
-      </c>
-      <c r="V366" s="3">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="U366" t="s">
+        <v>25</v>
       </c>
       <c r="X366" t="s">
         <v>41</v>
@@ -27180,19 +27153,19 @@
     </row>
     <row r="367" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B367">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C367">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D367">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E367" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F367" t="s">
         <v>43</v>
@@ -27201,46 +27174,49 @@
         <v>25</v>
       </c>
       <c r="H367">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I367">
-        <v>3492</v>
+        <v>6219</v>
       </c>
       <c r="J367">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="K367">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="L367">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M367">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N367">
         <v>0</v>
       </c>
       <c r="O367" s="2">
-        <v>4.2824074074074075E-4</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="P367" s="2">
-        <v>2.1990740740740742E-3</v>
+        <v>9.0277777777777774E-4</v>
       </c>
       <c r="Q367" s="3">
-        <v>2.69E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="R367" s="3">
-        <v>0.34039999999999998</v>
-      </c>
-      <c r="S367" s="3">
-        <v>0.875</v>
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="S367" s="4">
+        <v>1</v>
       </c>
       <c r="T367">
-        <v>0</v>
-      </c>
-      <c r="U367" s="4">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="U367" t="s">
+        <v>25</v>
+      </c>
+      <c r="V367" s="3">
+        <v>1</v>
       </c>
       <c r="X367" t="s">
         <v>41</v>
@@ -27251,16 +27227,16 @@
         <v>46182</v>
       </c>
       <c r="B368">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C368">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D368">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E368" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F368" t="s">
         <v>43</v>
@@ -27269,49 +27245,46 @@
         <v>25</v>
       </c>
       <c r="H368">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I368">
-        <v>18719</v>
+        <v>3712</v>
       </c>
       <c r="J368">
-        <v>232</v>
+        <v>87</v>
       </c>
       <c r="K368">
-        <v>3482</v>
+        <v>17</v>
       </c>
       <c r="L368">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M368">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N368">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O368" s="2">
-        <v>8.9120370370370373E-4</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="P368" s="2">
-        <v>1.2037037037037038E-3</v>
+        <v>1.3310185185185185E-3</v>
       </c>
       <c r="Q368" s="3">
-        <v>1.24E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="R368" s="3">
-        <v>15</v>
-      </c>
-      <c r="S368" s="3">
-        <v>4.5999999999999999E-3</v>
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="S368" s="4">
+        <v>1</v>
       </c>
       <c r="T368">
-        <v>3448</v>
-      </c>
-      <c r="U368" s="3">
-        <v>0.99480000000000002</v>
-      </c>
-      <c r="V368" s="3">
-        <v>0.95240000000000002</v>
+        <v>-11</v>
+      </c>
+      <c r="U368" t="s">
+        <v>25</v>
       </c>
       <c r="X368" t="s">
         <v>41</v>
@@ -27322,7 +27295,7 @@
         <v>46182</v>
       </c>
       <c r="B369">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C369">
         <v>81</v>
@@ -27340,49 +27313,49 @@
         <v>25</v>
       </c>
       <c r="H369">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I369">
-        <v>20163</v>
+        <v>11882</v>
       </c>
       <c r="J369">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="K369">
-        <v>2839</v>
+        <v>29</v>
       </c>
       <c r="L369">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M369">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N369">
         <v>0</v>
       </c>
       <c r="O369" s="2">
-        <v>8.9120370370370373E-4</v>
+        <v>7.9861111111111116E-4</v>
       </c>
       <c r="P369" s="2">
-        <v>9.3749999999999997E-4</v>
+        <v>1.9791666666666668E-3</v>
       </c>
       <c r="Q369" s="3">
-        <v>1.24E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="R369" s="3">
-        <v>11.35</v>
-      </c>
-      <c r="S369" s="3">
-        <v>7.0000000000000001E-3</v>
+        <v>0.1895</v>
+      </c>
+      <c r="S369" s="4">
+        <v>1</v>
       </c>
       <c r="T369">
-        <v>2793</v>
-      </c>
-      <c r="U369" s="3">
-        <v>0.99080000000000001</v>
+        <v>-16</v>
+      </c>
+      <c r="U369" t="s">
+        <v>25</v>
       </c>
       <c r="V369" s="3">
-        <v>0.85289999999999999</v>
+        <v>1</v>
       </c>
       <c r="X369" t="s">
         <v>41</v>
@@ -27393,16 +27366,16 @@
         <v>46182</v>
       </c>
       <c r="B370">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C370">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D370">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E370" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F370" t="s">
         <v>43</v>
@@ -27411,49 +27384,46 @@
         <v>25</v>
       </c>
       <c r="H370">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I370">
-        <v>12067</v>
+        <v>3434</v>
       </c>
       <c r="J370">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K370">
-        <v>3038</v>
+        <v>38</v>
       </c>
       <c r="L370">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="M370">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N370">
         <v>0</v>
       </c>
       <c r="O370" s="2">
-        <v>1.1226851851851851E-3</v>
+        <v>2.8935185185185184E-4</v>
       </c>
       <c r="P370" s="2">
-        <v>1.7824074074074075E-3</v>
-      </c>
-      <c r="Q370" s="4">
-        <v>0.01</v>
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="Q370" s="3">
+        <v>3.7900000000000003E-2</v>
       </c>
       <c r="R370" s="3">
-        <v>25.1</v>
-      </c>
-      <c r="S370" s="3">
-        <v>1.6000000000000001E-3</v>
+        <v>0.2923</v>
+      </c>
+      <c r="S370" s="4">
+        <v>1</v>
       </c>
       <c r="T370">
-        <v>3020</v>
-      </c>
-      <c r="U370" s="3">
-        <v>0.99570000000000003</v>
-      </c>
-      <c r="V370" s="3">
-        <v>1</v>
+        <v>-17</v>
+      </c>
+      <c r="U370" t="s">
+        <v>25</v>
       </c>
       <c r="X370" t="s">
         <v>41</v>
@@ -27464,16 +27434,16 @@
         <v>46182</v>
       </c>
       <c r="B371">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C371">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D371">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E371" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F371" t="s">
         <v>43</v>
@@ -27482,46 +27452,49 @@
         <v>25</v>
       </c>
       <c r="H371">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I371">
-        <v>8477</v>
+        <v>16923</v>
       </c>
       <c r="J371">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="K371">
-        <v>949</v>
+        <v>41</v>
       </c>
       <c r="L371">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M371">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="N371">
         <v>0</v>
       </c>
       <c r="O371" s="2">
-        <v>3.0092592592592595E-4</v>
+        <v>6.7129629629629625E-4</v>
       </c>
       <c r="P371" s="2">
-        <v>6.3657407407407413E-4</v>
+        <v>1.4467592592592592E-3</v>
       </c>
       <c r="Q371" s="3">
-        <v>3.7199999999999997E-2</v>
+        <v>1.55E-2</v>
       </c>
       <c r="R371" s="3">
-        <v>3.012</v>
-      </c>
-      <c r="S371" s="3">
-        <v>1.0500000000000001E-2</v>
+        <v>0.1565</v>
+      </c>
+      <c r="S371" s="4">
+        <v>1</v>
       </c>
       <c r="T371">
-        <v>881</v>
-      </c>
-      <c r="U371" s="3">
-        <v>0.93820000000000003</v>
+        <v>-29</v>
+      </c>
+      <c r="U371" t="s">
+        <v>25</v>
+      </c>
+      <c r="V371" s="3">
+        <v>1</v>
       </c>
       <c r="X371" t="s">
         <v>41</v>
@@ -27532,16 +27505,16 @@
         <v>46182</v>
       </c>
       <c r="B372">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C372">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D372">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E372" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F372" t="s">
         <v>43</v>
@@ -27550,49 +27523,46 @@
         <v>25</v>
       </c>
       <c r="H372">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I372">
-        <v>9021</v>
+        <v>3916</v>
       </c>
       <c r="J372">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="K372">
-        <v>2828</v>
+        <v>25</v>
       </c>
       <c r="L372">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="M372">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O372" s="2">
-        <v>1.1574074074074073E-3</v>
+        <v>3.4722222222222224E-4</v>
       </c>
       <c r="P372" s="2">
-        <v>1.4004629629629629E-3</v>
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="Q372" s="3">
-        <v>9.4000000000000004E-3</v>
+        <v>3.09E-2</v>
       </c>
       <c r="R372" s="3">
-        <v>33.270000000000003</v>
-      </c>
-      <c r="S372" s="3">
-        <v>2.5000000000000001E-3</v>
+        <v>0.20660000000000001</v>
+      </c>
+      <c r="S372" s="4">
+        <v>1</v>
       </c>
       <c r="T372">
-        <v>2811</v>
-      </c>
-      <c r="U372" s="3">
-        <v>0.99650000000000005</v>
-      </c>
-      <c r="V372" s="3">
-        <v>1</v>
+        <v>-15</v>
+      </c>
+      <c r="U372" t="s">
+        <v>25</v>
       </c>
       <c r="X372" t="s">
         <v>41</v>
@@ -27603,16 +27573,16 @@
         <v>46182</v>
       </c>
       <c r="B373">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C373">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D373">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E373" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F373" t="s">
         <v>43</v>
@@ -27621,46 +27591,49 @@
         <v>25</v>
       </c>
       <c r="H373">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I373">
-        <v>6627</v>
+        <v>17295</v>
       </c>
       <c r="J373">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="K373">
-        <v>511</v>
+        <v>45</v>
       </c>
       <c r="L373">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M373">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N373">
         <v>0</v>
       </c>
       <c r="O373" s="2">
-        <v>3.2407407407407406E-4</v>
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="P373" s="2">
-        <v>7.6388888888888893E-4</v>
+        <v>9.1435185185185185E-4</v>
       </c>
       <c r="Q373" s="3">
-        <v>3.5000000000000003E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="R373" s="3">
-        <v>2.202</v>
-      </c>
-      <c r="S373" s="3">
-        <v>7.2400000000000006E-2</v>
+        <v>0.15959999999999999</v>
+      </c>
+      <c r="S373" s="4">
+        <v>1</v>
       </c>
       <c r="T373">
-        <v>470</v>
-      </c>
-      <c r="U373" s="3">
-        <v>0.99160000000000004</v>
+        <v>-27</v>
+      </c>
+      <c r="U373" t="s">
+        <v>25</v>
+      </c>
+      <c r="V373" s="3">
+        <v>1</v>
       </c>
       <c r="X373" t="s">
         <v>41</v>
@@ -27671,16 +27644,16 @@
         <v>46182</v>
       </c>
       <c r="B374">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C374">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D374">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E374" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F374" t="s">
         <v>43</v>
@@ -27689,49 +27662,46 @@
         <v>25</v>
       </c>
       <c r="H374">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I374">
-        <v>14219</v>
+        <v>5345</v>
       </c>
       <c r="J374">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K374">
-        <v>3255</v>
+        <v>40</v>
       </c>
       <c r="L374">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M374">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="N374">
         <v>0</v>
       </c>
       <c r="O374" s="2">
-        <v>8.4490740740740739E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="P374" s="2">
-        <v>1.736111111111111E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="Q374" s="3">
-        <v>1.2800000000000001E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="R374" s="3">
-        <v>17.88</v>
-      </c>
-      <c r="S374" s="3">
-        <v>3.3999999999999998E-3</v>
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="S374" s="4">
+        <v>1</v>
       </c>
       <c r="T374">
-        <v>3230</v>
-      </c>
-      <c r="U374" s="3">
-        <v>0.99570000000000003</v>
-      </c>
-      <c r="V374" s="3">
-        <v>1</v>
+        <v>-28</v>
+      </c>
+      <c r="U374" t="s">
+        <v>25</v>
       </c>
       <c r="X374" t="s">
         <v>41</v>
@@ -27742,16 +27712,16 @@
         <v>46182</v>
       </c>
       <c r="B375">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C375">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D375">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E375" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F375" t="s">
         <v>43</v>
@@ -27760,46 +27730,49 @@
         <v>25</v>
       </c>
       <c r="H375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I375">
-        <v>4319</v>
+        <v>24262</v>
       </c>
       <c r="J375">
-        <v>123</v>
+        <v>261</v>
       </c>
       <c r="K375">
-        <v>524</v>
+        <v>59</v>
       </c>
       <c r="L375">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="M375">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N375">
         <v>0</v>
       </c>
       <c r="O375" s="2">
-        <v>3.9351851851851852E-4</v>
-      </c>
-      <c r="P375" s="2">
-        <v>5.3240740740740744E-4</v>
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="P375" t="s">
+        <v>24</v>
       </c>
       <c r="Q375" s="3">
-        <v>2.8500000000000001E-2</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="R375" s="3">
-        <v>4.26</v>
-      </c>
-      <c r="S375" s="3">
-        <v>1.15E-2</v>
+        <v>0.2261</v>
+      </c>
+      <c r="S375" s="4">
+        <v>1</v>
       </c>
       <c r="T375">
-        <v>507</v>
-      </c>
-      <c r="U375" s="3">
-        <v>0.9788</v>
+        <v>0</v>
+      </c>
+      <c r="U375" t="s">
+        <v>25</v>
+      </c>
+      <c r="V375" s="3">
+        <v>1</v>
       </c>
       <c r="X375" t="s">
         <v>41</v>
@@ -27810,16 +27783,16 @@
         <v>46182</v>
       </c>
       <c r="B376">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C376">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D376">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E376" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F376" t="s">
         <v>43</v>
@@ -27828,49 +27801,46 @@
         <v>25</v>
       </c>
       <c r="H376">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I376">
-        <v>6219</v>
+        <v>8288</v>
       </c>
       <c r="J376">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="K376">
-        <v>1917</v>
+        <v>53</v>
       </c>
       <c r="L376">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="M376">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N376">
         <v>0</v>
       </c>
       <c r="O376" s="2">
-        <v>9.1435185185185185E-4</v>
-      </c>
-      <c r="P376" s="2">
-        <v>9.0277777777777774E-4</v>
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P376" t="s">
+        <v>24</v>
       </c>
       <c r="Q376" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="R376" s="3">
-        <v>26.62</v>
-      </c>
-      <c r="S376" s="3">
-        <v>3.0999999999999999E-3</v>
+        <v>0.2208</v>
+      </c>
+      <c r="S376" s="4">
+        <v>1</v>
       </c>
       <c r="T376">
-        <v>1904</v>
-      </c>
-      <c r="U376" s="3">
-        <v>0.99629999999999996</v>
-      </c>
-      <c r="V376" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U376" t="s">
+        <v>25</v>
       </c>
       <c r="X376" t="s">
         <v>41</v>
@@ -27881,16 +27851,16 @@
         <v>46182</v>
       </c>
       <c r="B377">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C377">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D377">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E377" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F377" t="s">
         <v>43</v>
@@ -27899,46 +27869,49 @@
         <v>25</v>
       </c>
       <c r="H377">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I377">
-        <v>3712</v>
+        <v>28325</v>
       </c>
       <c r="J377">
-        <v>87</v>
+        <v>277</v>
       </c>
       <c r="K377">
-        <v>244</v>
+        <v>38</v>
       </c>
       <c r="L377">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="M377">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N377">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O377" s="2">
-        <v>4.7453703703703704E-4</v>
-      </c>
-      <c r="P377" s="2">
-        <v>1.3310185185185185E-3</v>
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P377" t="s">
+        <v>24</v>
       </c>
       <c r="Q377" s="3">
-        <v>2.3400000000000001E-2</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="R377" s="3">
-        <v>2.8039999999999998</v>
-      </c>
-      <c r="S377" s="3">
-        <v>2.46E-2</v>
+        <v>0.13719999999999999</v>
+      </c>
+      <c r="S377" s="4">
+        <v>1</v>
       </c>
       <c r="T377">
-        <v>227</v>
-      </c>
-      <c r="U377" s="3">
-        <v>0.95379999999999998</v>
+        <v>0</v>
+      </c>
+      <c r="U377" t="s">
+        <v>25</v>
+      </c>
+      <c r="V377" t="s">
+        <v>25</v>
       </c>
       <c r="X377" t="s">
         <v>41</v>
@@ -27949,16 +27922,16 @@
         <v>46182</v>
       </c>
       <c r="B378">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C378">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D378">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E378" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F378" t="s">
         <v>43</v>
@@ -27967,49 +27940,46 @@
         <v>25</v>
       </c>
       <c r="H378">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I378">
-        <v>11882</v>
+        <v>10294</v>
       </c>
       <c r="J378">
-        <v>153</v>
+        <v>298</v>
       </c>
       <c r="K378">
-        <v>3147</v>
+        <v>65</v>
       </c>
       <c r="L378">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="M378">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N378">
         <v>0</v>
       </c>
       <c r="O378" s="2">
-        <v>7.9861111111111116E-4</v>
-      </c>
-      <c r="P378" s="2">
-        <v>1.9791666666666668E-3</v>
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P378" t="s">
+        <v>24</v>
       </c>
       <c r="Q378" s="3">
-        <v>1.29E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="R378" s="3">
-        <v>20.56</v>
-      </c>
-      <c r="S378" s="3">
-        <v>4.4000000000000003E-3</v>
+        <v>0.21809999999999999</v>
+      </c>
+      <c r="S378" s="4">
+        <v>1</v>
       </c>
       <c r="T378">
-        <v>3117</v>
-      </c>
-      <c r="U378" s="3">
-        <v>0.99490000000000001</v>
-      </c>
-      <c r="V378" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U378" t="s">
+        <v>25</v>
       </c>
       <c r="X378" t="s">
         <v>41</v>
@@ -28020,64 +27990,64 @@
         <v>46182</v>
       </c>
       <c r="B379">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C379">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D379">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E379" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F379" t="s">
         <v>43</v>
       </c>
       <c r="G379">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H379">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I379">
-        <v>3434</v>
+        <v>246</v>
       </c>
       <c r="J379">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K379">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="L379">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M379">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N379">
         <v>0</v>
       </c>
       <c r="O379" s="2">
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="P379" s="2">
-        <v>4.7453703703703704E-4</v>
+        <v>2.8240740740740739E-3</v>
+      </c>
+      <c r="P379" t="s">
+        <v>24</v>
       </c>
       <c r="Q379" s="3">
-        <v>3.7900000000000003E-2</v>
-      </c>
-      <c r="R379" s="3">
-        <v>5.5609999999999999</v>
-      </c>
-      <c r="S379" s="3">
-        <v>2.9000000000000001E-2</v>
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="R379" s="4">
+        <v>0</v>
+      </c>
+      <c r="S379" t="s">
+        <v>25</v>
       </c>
       <c r="T379">
-        <v>685</v>
-      </c>
-      <c r="U379" s="3">
-        <v>0.9758</v>
+        <v>0</v>
+      </c>
+      <c r="U379" t="s">
+        <v>25</v>
       </c>
       <c r="X379" t="s">
         <v>41</v>
@@ -28088,67 +28058,64 @@
         <v>46182</v>
       </c>
       <c r="B380">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C380">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D380">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E380" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F380" t="s">
         <v>43</v>
       </c>
       <c r="G380">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H380">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I380">
-        <v>16923</v>
+        <v>165</v>
       </c>
       <c r="J380">
-        <v>262</v>
+        <v>3</v>
       </c>
       <c r="K380">
-        <v>3217</v>
+        <v>0</v>
       </c>
       <c r="L380">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M380">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N380">
         <v>0</v>
       </c>
       <c r="O380" s="2">
-        <v>6.7129629629629625E-4</v>
-      </c>
-      <c r="P380" s="2">
-        <v>1.4467592592592592E-3</v>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P380" t="s">
+        <v>24</v>
       </c>
       <c r="Q380" s="3">
-        <v>1.55E-2</v>
-      </c>
-      <c r="R380" s="3">
-        <v>12.27</v>
-      </c>
-      <c r="S380" s="3">
-        <v>4.0000000000000001E-3</v>
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="R380" s="4">
+        <v>0</v>
+      </c>
+      <c r="S380" t="s">
+        <v>25</v>
       </c>
       <c r="T380">
-        <v>3175</v>
-      </c>
-      <c r="U380" s="3">
-        <v>0.9909</v>
-      </c>
-      <c r="V380" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U380" t="s">
+        <v>25</v>
       </c>
       <c r="X380" t="s">
         <v>41</v>
@@ -28156,19 +28123,19 @@
     </row>
     <row r="381" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B381">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C381">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D381">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E381" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F381" t="s">
         <v>43</v>
@@ -28177,46 +28144,49 @@
         <v>25</v>
       </c>
       <c r="H381">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I381">
-        <v>3916</v>
+        <v>11322</v>
       </c>
       <c r="J381">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="K381">
-        <v>1057</v>
+        <v>35</v>
       </c>
       <c r="L381">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="M381">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N381">
         <v>0</v>
       </c>
       <c r="O381" s="2">
-        <v>3.4722222222222224E-4</v>
-      </c>
-      <c r="P381" s="2">
-        <v>5.0925925925925921E-4</v>
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P381" t="s">
+        <v>24</v>
       </c>
       <c r="Q381" s="3">
-        <v>3.09E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="R381" s="3">
-        <v>8.7349999999999994</v>
-      </c>
-      <c r="S381" s="3">
-        <v>9.4999999999999998E-3</v>
+        <v>0.1852</v>
+      </c>
+      <c r="S381" s="4">
+        <v>1</v>
       </c>
       <c r="T381">
-        <v>1032</v>
-      </c>
-      <c r="U381" s="3">
-        <v>0.98570000000000002</v>
+        <v>0</v>
+      </c>
+      <c r="U381" t="s">
+        <v>25</v>
+      </c>
+      <c r="V381" t="s">
+        <v>25</v>
       </c>
       <c r="X381" t="s">
         <v>41</v>
@@ -28224,19 +28194,19 @@
     </row>
     <row r="382" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B382">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C382">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D382">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E382" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F382" t="s">
         <v>43</v>
@@ -28245,49 +28215,46 @@
         <v>25</v>
       </c>
       <c r="H382">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I382">
-        <v>17295</v>
+        <v>4604</v>
       </c>
       <c r="J382">
-        <v>282</v>
+        <v>139</v>
       </c>
       <c r="K382">
-        <v>3228</v>
+        <v>33</v>
       </c>
       <c r="L382">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="M382">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N382">
         <v>0</v>
       </c>
       <c r="O382" s="2">
-        <v>6.5972222222222224E-4</v>
-      </c>
-      <c r="P382" s="2">
-        <v>9.1435185185185185E-4</v>
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P382" t="s">
+        <v>24</v>
       </c>
       <c r="Q382" s="3">
-        <v>1.6299999999999999E-2</v>
+        <v>3.0200000000000001E-2</v>
       </c>
       <c r="R382" s="3">
-        <v>11.44</v>
-      </c>
-      <c r="S382" s="3">
-        <v>5.5999999999999999E-3</v>
+        <v>0.2374</v>
+      </c>
+      <c r="S382" s="4">
+        <v>1</v>
       </c>
       <c r="T382">
-        <v>3183</v>
-      </c>
-      <c r="U382" s="3">
-        <v>0.99160000000000004</v>
-      </c>
-      <c r="V382" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U382" t="s">
+        <v>25</v>
       </c>
       <c r="X382" t="s">
         <v>41</v>
@@ -28295,19 +28262,19 @@
     </row>
     <row r="383" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B383">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C383">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D383">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E383" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F383" t="s">
         <v>43</v>
@@ -28316,46 +28283,49 @@
         <v>25</v>
       </c>
       <c r="H383">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I383">
-        <v>5345</v>
+        <v>7174</v>
       </c>
       <c r="J383">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="K383">
-        <v>1073</v>
+        <v>26</v>
       </c>
       <c r="L383">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M383">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O383" s="2">
-        <v>3.0092592592592595E-4</v>
+        <v>9.0277777777777774E-4</v>
       </c>
       <c r="P383" s="2">
-        <v>4.0509259259259258E-4</v>
+        <v>1.1111111111111111E-3</v>
       </c>
       <c r="Q383" s="3">
-        <v>3.5900000000000001E-2</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="R383" s="3">
-        <v>5.5880000000000001</v>
-      </c>
-      <c r="S383" s="3">
-        <v>1.21E-2</v>
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="S383" s="4">
+        <v>1</v>
       </c>
       <c r="T383">
-        <v>1032</v>
-      </c>
-      <c r="U383" s="3">
-        <v>0.97360000000000002</v>
+        <v>-18</v>
+      </c>
+      <c r="U383" t="s">
+        <v>25</v>
+      </c>
+      <c r="V383" s="3">
+        <v>1</v>
       </c>
       <c r="X383" t="s">
         <v>41</v>
@@ -28363,19 +28333,19 @@
     </row>
     <row r="384" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B384">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C384">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D384">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E384" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F384" t="s">
         <v>43</v>
@@ -28384,49 +28354,46 @@
         <v>25</v>
       </c>
       <c r="H384">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I384">
-        <v>24262</v>
+        <v>7018</v>
       </c>
       <c r="J384">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="K384">
-        <v>1314</v>
+        <v>44</v>
       </c>
       <c r="L384">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M384">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N384">
         <v>0</v>
       </c>
       <c r="O384" s="2">
-        <v>1.0532407407407407E-3</v>
-      </c>
-      <c r="P384" t="s">
-        <v>24</v>
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P384" s="2">
+        <v>6.018518518518519E-4</v>
       </c>
       <c r="Q384" s="3">
-        <v>1.0800000000000001E-2</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="R384" s="3">
-        <v>5.0339999999999998</v>
-      </c>
-      <c r="S384" s="3">
-        <v>2.4400000000000002E-2</v>
+        <v>0.2404</v>
+      </c>
+      <c r="S384" s="4">
+        <v>1</v>
       </c>
       <c r="T384">
-        <v>1282</v>
-      </c>
-      <c r="U384" s="4">
-        <v>1</v>
-      </c>
-      <c r="V384" s="3">
-        <v>1</v>
+        <v>-41</v>
+      </c>
+      <c r="U384" t="s">
+        <v>25</v>
       </c>
       <c r="X384" t="s">
         <v>41</v>
@@ -28434,19 +28401,19 @@
     </row>
     <row r="385" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B385">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C385">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D385">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E385" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F385" t="s">
         <v>43</v>
@@ -28455,45 +28422,48 @@
         <v>25</v>
       </c>
       <c r="H385">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I385">
-        <v>8288</v>
+        <v>14655</v>
       </c>
       <c r="J385">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="K385">
-        <v>552</v>
+        <v>33</v>
       </c>
       <c r="L385">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="M385">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N385">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O385" s="2">
-        <v>3.8194444444444446E-4</v>
-      </c>
-      <c r="P385" t="s">
-        <v>24</v>
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P385" s="2">
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="Q385" s="3">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="R385" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="S385" s="3">
-        <v>3.2599999999999997E-2</v>
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R385" s="3">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="S385" s="4">
+        <v>1</v>
       </c>
       <c r="T385">
-        <v>534</v>
-      </c>
-      <c r="U385" s="4">
+        <v>-19</v>
+      </c>
+      <c r="U385" t="s">
+        <v>25</v>
+      </c>
+      <c r="V385" s="3">
         <v>1</v>
       </c>
       <c r="X385" t="s">
@@ -28502,19 +28472,19 @@
     </row>
     <row r="386" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B386">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C386">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D386">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E386" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F386" t="s">
         <v>43</v>
@@ -28523,48 +28493,45 @@
         <v>25</v>
       </c>
       <c r="H386">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I386">
-        <v>28325</v>
+        <v>5338</v>
       </c>
       <c r="J386">
-        <v>277</v>
+        <v>127</v>
       </c>
       <c r="K386">
-        <v>2341</v>
+        <v>34</v>
       </c>
       <c r="L386">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M386">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N386">
         <v>0</v>
       </c>
       <c r="O386" s="2">
-        <v>1.1458333333333333E-3</v>
-      </c>
-      <c r="P386" t="s">
-        <v>24</v>
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P386" s="2">
+        <v>6.5972222222222224E-4</v>
       </c>
       <c r="Q386" s="3">
-        <v>9.7999999999999997E-3</v>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="R386" s="3">
-        <v>8.4510000000000005</v>
-      </c>
-      <c r="S386" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>0.26769999999999999</v>
+      </c>
+      <c r="S386" s="4">
+        <v>1</v>
       </c>
       <c r="T386">
-        <v>2326</v>
-      </c>
-      <c r="U386" s="4">
-        <v>1</v>
-      </c>
-      <c r="V386" t="s">
+        <v>-25</v>
+      </c>
+      <c r="U386" t="s">
         <v>25</v>
       </c>
       <c r="X386" t="s">
@@ -28573,19 +28540,19 @@
     </row>
     <row r="387" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B387">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C387">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D387">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E387" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F387" t="s">
         <v>43</v>
@@ -28594,45 +28561,48 @@
         <v>25</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I387">
-        <v>10294</v>
+        <v>16328</v>
       </c>
       <c r="J387">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="K387">
-        <v>1075</v>
+        <v>40</v>
       </c>
       <c r="L387">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="M387">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N387">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O387" s="2">
-        <v>3.8194444444444446E-4</v>
-      </c>
-      <c r="P387" t="s">
-        <v>24</v>
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="P387" s="2">
+        <v>1.2962962962962963E-3</v>
       </c>
       <c r="Q387" s="3">
-        <v>2.8899999999999999E-2</v>
+        <v>1.11E-2</v>
       </c>
       <c r="R387" s="3">
-        <v>3.6070000000000002</v>
-      </c>
-      <c r="S387" s="3">
-        <v>1.49E-2</v>
+        <v>0.221</v>
+      </c>
+      <c r="S387" s="4">
+        <v>1</v>
       </c>
       <c r="T387">
-        <v>1059</v>
-      </c>
-      <c r="U387" s="4">
+        <v>-24</v>
+      </c>
+      <c r="U387" t="s">
+        <v>25</v>
+      </c>
+      <c r="V387" s="3">
         <v>1</v>
       </c>
       <c r="X387" t="s">
@@ -28641,67 +28611,67 @@
     </row>
     <row r="388" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B388">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C388">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D388">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E388" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F388" t="s">
         <v>43</v>
       </c>
       <c r="G388">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H388">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I388">
-        <v>246</v>
+        <v>2369</v>
       </c>
       <c r="J388">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="K388">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="L388">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M388">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N388">
         <v>0</v>
       </c>
       <c r="O388" s="2">
-        <v>2.8240740740740739E-3</v>
-      </c>
-      <c r="P388" t="s">
-        <v>24</v>
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="P388" s="2">
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="Q388" s="3">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="R388" s="4">
-        <v>39</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="R388" s="3">
+        <v>0.15379999999999999</v>
       </c>
       <c r="S388" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T388">
-        <v>39</v>
-      </c>
-      <c r="U388" s="4">
-        <v>1</v>
+        <v>-3</v>
+      </c>
+      <c r="U388" t="s">
+        <v>25</v>
       </c>
       <c r="X388" t="s">
         <v>41</v>
@@ -28709,66 +28679,69 @@
     </row>
     <row r="389" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B389">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C389">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D389">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E389" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F389" t="s">
         <v>43</v>
       </c>
       <c r="G389">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H389">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I389">
-        <v>165</v>
+        <v>17098</v>
       </c>
       <c r="J389">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="K389">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="L389">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M389">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N389">
         <v>0</v>
       </c>
       <c r="O389" s="2">
-        <v>6.2500000000000001E-4</v>
-      </c>
-      <c r="P389" t="s">
-        <v>24</v>
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="P389" s="2">
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="Q389" s="3">
-        <v>1.8200000000000001E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="R389" s="3">
-        <v>7.3330000000000002</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="S389" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T389">
-        <v>22</v>
-      </c>
-      <c r="U389" s="4">
+        <v>-17</v>
+      </c>
+      <c r="U389" t="s">
+        <v>25</v>
+      </c>
+      <c r="V389" s="3">
         <v>1</v>
       </c>
       <c r="X389" t="s">
@@ -28780,16 +28753,16 @@
         <v>46183</v>
       </c>
       <c r="B390">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C390">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D390">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E390" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F390" t="s">
         <v>43</v>
@@ -28801,16 +28774,16 @@
         <v>0</v>
       </c>
       <c r="I390">
-        <v>11322</v>
+        <v>2068</v>
       </c>
       <c r="J390">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="K390">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="L390">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M390">
         <v>0</v>
@@ -28819,27 +28792,24 @@
         <v>0</v>
       </c>
       <c r="O390" s="2">
-        <v>6.8287037037037036E-4</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="P390" t="s">
         <v>24</v>
       </c>
       <c r="Q390" s="3">
-        <v>1.67E-2</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="R390" s="3">
-        <v>1.121</v>
-      </c>
-      <c r="S390" s="3">
-        <v>5.6599999999999998E-2</v>
+        <v>0.26529999999999998</v>
+      </c>
+      <c r="S390" s="4">
+        <v>1</v>
       </c>
       <c r="T390">
-        <v>200</v>
-      </c>
-      <c r="U390" s="4">
-        <v>1</v>
-      </c>
-      <c r="V390" t="s">
+        <v>0</v>
+      </c>
+      <c r="U390" t="s">
         <v>25</v>
       </c>
       <c r="X390" t="s">
@@ -28851,16 +28821,16 @@
         <v>46183</v>
       </c>
       <c r="B391">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C391">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D391">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E391" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F391" t="s">
         <v>43</v>
@@ -28869,45 +28839,48 @@
         <v>25</v>
       </c>
       <c r="H391">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I391">
-        <v>4604</v>
+        <v>18676</v>
       </c>
       <c r="J391">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K391">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="L391">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="M391">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N391">
         <v>0</v>
       </c>
       <c r="O391" s="2">
-        <v>3.7037037037037035E-4</v>
-      </c>
-      <c r="P391" t="s">
-        <v>24</v>
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="P391" s="2">
+        <v>1.0532407407407407E-3</v>
       </c>
       <c r="Q391" s="3">
-        <v>3.0200000000000001E-2</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="R391" s="3">
-        <v>0.74819999999999998</v>
-      </c>
-      <c r="S391" s="3">
-        <v>6.7299999999999999E-2</v>
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="S391" s="4">
+        <v>1</v>
       </c>
       <c r="T391">
-        <v>97</v>
-      </c>
-      <c r="U391" s="4">
+        <v>-19</v>
+      </c>
+      <c r="U391" t="s">
+        <v>25</v>
+      </c>
+      <c r="V391" s="3">
         <v>1</v>
       </c>
       <c r="X391" t="s">
@@ -28919,67 +28892,64 @@
         <v>46183</v>
       </c>
       <c r="B392">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C392">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D392">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E392" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F392" t="s">
         <v>43</v>
       </c>
       <c r="G392">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H392">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I392">
-        <v>7174</v>
+        <v>922</v>
       </c>
       <c r="J392">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="K392">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L392">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M392">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O392" s="2">
-        <v>9.0277777777777774E-4</v>
-      </c>
-      <c r="P392" s="2">
-        <v>1.1111111111111111E-3</v>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P392" t="s">
+        <v>24</v>
       </c>
       <c r="Q392" s="3">
-        <v>1.2699999999999999E-2</v>
-      </c>
-      <c r="R392" s="3">
-        <v>0.32969999999999999</v>
-      </c>
-      <c r="S392" s="3">
-        <v>0.36670000000000003</v>
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="R392" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="S392" s="4">
+        <v>1</v>
       </c>
       <c r="T392">
-        <v>1</v>
-      </c>
-      <c r="U392" s="3">
-        <v>5.2600000000000001E-2</v>
-      </c>
-      <c r="V392" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U392" t="s">
+        <v>25</v>
       </c>
       <c r="X392" t="s">
         <v>41</v>
@@ -28990,16 +28960,16 @@
         <v>46183</v>
       </c>
       <c r="B393">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C393">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D393">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E393" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F393" t="s">
         <v>43</v>
@@ -29008,46 +28978,49 @@
         <v>25</v>
       </c>
       <c r="H393">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I393">
-        <v>7018</v>
+        <v>18370</v>
       </c>
       <c r="J393">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K393">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="L393">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="M393">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="N393">
         <v>0</v>
       </c>
       <c r="O393" s="2">
-        <v>4.3981481481481481E-4</v>
+        <v>1.1342592592592593E-3</v>
       </c>
       <c r="P393" s="2">
-        <v>6.018518518518519E-4</v>
+        <v>1.1111111111111111E-3</v>
       </c>
       <c r="Q393" s="3">
-        <v>2.6100000000000002E-2</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="R393" s="3">
-        <v>0.25679999999999997</v>
-      </c>
-      <c r="S393" s="3">
-        <v>0.10639999999999999</v>
+        <v>0.1593</v>
+      </c>
+      <c r="S393" s="4">
+        <v>1</v>
       </c>
       <c r="T393">
-        <v>1</v>
-      </c>
-      <c r="U393" s="3">
-        <v>2.3800000000000002E-2</v>
+        <v>-15</v>
+      </c>
+      <c r="U393" t="s">
+        <v>25</v>
+      </c>
+      <c r="V393" s="3">
+        <v>0.9</v>
       </c>
       <c r="X393" t="s">
         <v>41</v>
@@ -29058,16 +29031,16 @@
         <v>46183</v>
       </c>
       <c r="B394">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C394">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D394">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E394" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F394" t="s">
         <v>43</v>
@@ -29076,49 +29049,46 @@
         <v>25</v>
       </c>
       <c r="H394">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I394">
-        <v>14655</v>
+        <v>2302</v>
       </c>
       <c r="J394">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="K394">
-        <v>3436</v>
+        <v>20</v>
       </c>
       <c r="L394">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M394">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N394">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O394" s="2">
-        <v>9.837962962962962E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="P394" s="2">
-        <v>1.5740740740740741E-3</v>
+        <v>8.4490740740740739E-4</v>
       </c>
       <c r="Q394" s="3">
-        <v>1.0999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="R394" s="3">
-        <v>21.34</v>
-      </c>
-      <c r="S394" s="3">
-        <v>4.8999999999999998E-3</v>
+        <v>0.21279999999999999</v>
+      </c>
+      <c r="S394" s="4">
+        <v>1</v>
       </c>
       <c r="T394">
-        <v>3400</v>
-      </c>
-      <c r="U394" s="3">
-        <v>0.99439999999999995</v>
-      </c>
-      <c r="V394" s="3">
-        <v>1</v>
+        <v>-15</v>
+      </c>
+      <c r="U394" t="s">
+        <v>25</v>
       </c>
       <c r="X394" t="s">
         <v>41</v>
@@ -29129,16 +29099,16 @@
         <v>46183</v>
       </c>
       <c r="B395">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C395">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D395">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E395" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F395" t="s">
         <v>43</v>
@@ -29150,43 +29120,46 @@
         <v>8</v>
       </c>
       <c r="I395">
-        <v>5338</v>
+        <v>14762</v>
       </c>
       <c r="J395">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="K395">
-        <v>1262</v>
+        <v>29</v>
       </c>
       <c r="L395">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="M395">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O395" s="2">
-        <v>4.5138888888888887E-4</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="P395" s="2">
-        <v>6.5972222222222224E-4</v>
+        <v>1.4930555555555556E-3</v>
       </c>
       <c r="Q395" s="3">
-        <v>2.3800000000000002E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="R395" s="3">
-        <v>9.9369999999999994</v>
-      </c>
-      <c r="S395" s="3">
-        <v>7.1000000000000004E-3</v>
+        <v>0.1696</v>
+      </c>
+      <c r="S395" s="4">
+        <v>1</v>
       </c>
       <c r="T395">
-        <v>1228</v>
-      </c>
-      <c r="U395" s="4">
-        <v>0.98</v>
+        <v>-18</v>
+      </c>
+      <c r="U395" t="s">
+        <v>25</v>
+      </c>
+      <c r="V395" s="3">
+        <v>1</v>
       </c>
       <c r="X395" t="s">
         <v>41</v>
@@ -29197,16 +29170,16 @@
         <v>46183</v>
       </c>
       <c r="B396">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C396">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D396">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E396" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F396" t="s">
         <v>43</v>
@@ -29215,49 +29188,46 @@
         <v>25</v>
       </c>
       <c r="H396">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I396">
-        <v>16328</v>
+        <v>5623</v>
       </c>
       <c r="J396">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="K396">
-        <v>3683</v>
+        <v>37</v>
       </c>
       <c r="L396">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="M396">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N396">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O396" s="2">
-        <v>9.7222222222222219E-4</v>
+        <v>3.9351851851851852E-4</v>
       </c>
       <c r="P396" s="2">
-        <v>1.2962962962962963E-3</v>
+        <v>4.1666666666666669E-4</v>
       </c>
       <c r="Q396" s="3">
-        <v>1.11E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="R396" s="3">
-        <v>20.34</v>
-      </c>
-      <c r="S396" s="3">
-        <v>4.8999999999999998E-3</v>
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="S396" s="4">
+        <v>1</v>
       </c>
       <c r="T396">
-        <v>3641</v>
-      </c>
-      <c r="U396" s="3">
-        <v>0.99350000000000005</v>
-      </c>
-      <c r="V396" s="3">
-        <v>1</v>
+        <v>-30</v>
+      </c>
+      <c r="U396" t="s">
+        <v>25</v>
       </c>
       <c r="X396" t="s">
         <v>41</v>
@@ -29268,16 +29238,16 @@
         <v>46183</v>
       </c>
       <c r="B397">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C397">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D397">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E397" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F397" t="s">
         <v>43</v>
@@ -29286,46 +29256,49 @@
         <v>25</v>
       </c>
       <c r="H397">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I397">
-        <v>2369</v>
+        <v>16376</v>
       </c>
       <c r="J397">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="K397">
-        <v>521</v>
+        <v>41</v>
       </c>
       <c r="L397">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="M397">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N397">
         <v>0</v>
       </c>
       <c r="O397" s="2">
-        <v>4.9768518518518521E-4</v>
+        <v>1.1921296296296296E-3</v>
       </c>
       <c r="P397" s="2">
-        <v>7.291666666666667E-4</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="Q397" s="3">
-        <v>2.1999999999999999E-2</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="R397" s="3">
-        <v>10.01</v>
-      </c>
-      <c r="S397" s="3">
-        <v>3.8E-3</v>
+        <v>0.2611</v>
+      </c>
+      <c r="S397" s="4">
+        <v>1</v>
       </c>
       <c r="T397">
-        <v>516</v>
-      </c>
-      <c r="U397" s="3">
-        <v>0.99419999999999997</v>
+        <v>-11</v>
+      </c>
+      <c r="U397" t="s">
+        <v>25</v>
+      </c>
+      <c r="V397" s="3">
+        <v>1</v>
       </c>
       <c r="X397" t="s">
         <v>41</v>
@@ -29336,16 +29309,16 @@
         <v>46183</v>
       </c>
       <c r="B398">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C398">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D398">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E398" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F398" t="s">
         <v>43</v>
@@ -29354,49 +29327,46 @@
         <v>25</v>
       </c>
       <c r="H398">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I398">
-        <v>17098</v>
+        <v>8943</v>
       </c>
       <c r="J398">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="K398">
-        <v>3426</v>
+        <v>65</v>
       </c>
       <c r="L398">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="M398">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="N398">
         <v>0</v>
       </c>
       <c r="O398" s="2">
-        <v>1.1805555555555556E-3</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="P398" s="2">
-        <v>1.5625000000000001E-3</v>
+        <v>4.5138888888888887E-4</v>
       </c>
       <c r="Q398" s="3">
-        <v>9.1999999999999998E-3</v>
+        <v>2.8299999999999999E-2</v>
       </c>
       <c r="R398" s="3">
-        <v>21.82</v>
-      </c>
-      <c r="S398" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>0.25690000000000002</v>
+      </c>
+      <c r="S398" s="4">
+        <v>1</v>
       </c>
       <c r="T398">
-        <v>3387</v>
-      </c>
-      <c r="U398" s="3">
-        <v>0.995</v>
-      </c>
-      <c r="V398" s="3">
-        <v>1</v>
+        <v>-40</v>
+      </c>
+      <c r="U398" t="s">
+        <v>25</v>
       </c>
       <c r="X398" t="s">
         <v>41</v>
@@ -29407,16 +29377,16 @@
         <v>46183</v>
       </c>
       <c r="B399">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C399">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D399">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E399" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F399" t="s">
         <v>43</v>
@@ -29425,45 +29395,48 @@
         <v>25</v>
       </c>
       <c r="H399">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I399">
-        <v>2068</v>
+        <v>17306</v>
       </c>
       <c r="J399">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="K399">
-        <v>441</v>
+        <v>28</v>
       </c>
       <c r="L399">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="M399">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N399">
         <v>0</v>
       </c>
       <c r="O399" s="2">
-        <v>4.5138888888888887E-4</v>
-      </c>
-      <c r="P399" t="s">
-        <v>24</v>
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="P399" s="2">
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="Q399" s="3">
-        <v>2.3699999999999999E-2</v>
-      </c>
-      <c r="R399" s="4">
-        <v>9</v>
-      </c>
-      <c r="S399" s="3">
-        <v>1.1299999999999999E-2</v>
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="R399" s="3">
+        <v>0.23930000000000001</v>
+      </c>
+      <c r="S399" s="4">
+        <v>1</v>
       </c>
       <c r="T399">
-        <v>436</v>
-      </c>
-      <c r="U399" s="4">
+        <v>-11</v>
+      </c>
+      <c r="U399" t="s">
+        <v>25</v>
+      </c>
+      <c r="V399" s="3">
         <v>1</v>
       </c>
       <c r="X399" t="s">
@@ -29475,16 +29448,16 @@
         <v>46183</v>
       </c>
       <c r="B400">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C400">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D400">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E400" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F400" t="s">
         <v>43</v>
@@ -29493,49 +29466,46 @@
         <v>25</v>
       </c>
       <c r="H400">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I400">
-        <v>18676</v>
+        <v>6585</v>
       </c>
       <c r="J400">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K400">
-        <v>2905</v>
+        <v>39</v>
       </c>
       <c r="L400">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="M400">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N400">
         <v>0</v>
       </c>
       <c r="O400" s="2">
-        <v>1.2962962962962963E-3</v>
+        <v>4.7453703703703704E-4</v>
       </c>
       <c r="P400" s="2">
-        <v>1.0532407407407407E-3</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="Q400" s="3">
-        <v>8.3999999999999995E-3</v>
+        <v>2.41E-2</v>
       </c>
       <c r="R400" s="3">
-        <v>18.5</v>
-      </c>
-      <c r="S400" s="3">
-        <v>7.1999999999999998E-3</v>
+        <v>0.24529999999999999</v>
+      </c>
+      <c r="S400" s="4">
+        <v>1</v>
       </c>
       <c r="T400">
-        <v>2865</v>
-      </c>
-      <c r="U400" s="3">
-        <v>0.99339999999999995</v>
-      </c>
-      <c r="V400" s="3">
-        <v>1</v>
+        <v>-13</v>
+      </c>
+      <c r="U400" t="s">
+        <v>25</v>
       </c>
       <c r="X400" t="s">
         <v>41</v>
@@ -29546,37 +29516,37 @@
         <v>46183</v>
       </c>
       <c r="B401">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C401">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D401">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E401" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F401" t="s">
         <v>43</v>
       </c>
       <c r="G401">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H401">
         <v>0</v>
       </c>
       <c r="I401">
-        <v>922</v>
+        <v>133</v>
       </c>
       <c r="J401">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K401">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="L401">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M401">
         <v>0</v>
@@ -29584,26 +29554,29 @@
       <c r="N401">
         <v>0</v>
       </c>
-      <c r="O401" s="2">
-        <v>6.2500000000000001E-4</v>
+      <c r="O401" t="s">
+        <v>24</v>
       </c>
       <c r="P401" t="s">
         <v>24</v>
       </c>
-      <c r="Q401" s="3">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="R401" s="3">
-        <v>8.5619999999999994</v>
-      </c>
-      <c r="S401" s="3">
-        <v>7.3000000000000001E-3</v>
+      <c r="Q401" s="4">
+        <v>0</v>
+      </c>
+      <c r="R401" t="s">
+        <v>25</v>
+      </c>
+      <c r="S401" t="s">
+        <v>25</v>
       </c>
       <c r="T401">
-        <v>136</v>
-      </c>
-      <c r="U401" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U401" t="s">
+        <v>25</v>
+      </c>
+      <c r="V401" t="s">
+        <v>25</v>
       </c>
       <c r="X401" t="s">
         <v>41</v>
@@ -29614,67 +29587,64 @@
         <v>46183</v>
       </c>
       <c r="B402">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C402">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D402">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E402" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F402" t="s">
         <v>43</v>
       </c>
       <c r="G402">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H402">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I402">
-        <v>18370</v>
+        <v>32</v>
       </c>
       <c r="J402">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="K402">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="L402">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M402">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N402">
         <v>0</v>
       </c>
       <c r="O402" s="2">
-        <v>1.1342592592592593E-3</v>
-      </c>
-      <c r="P402" s="2">
-        <v>1.1111111111111111E-3</v>
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="P402" t="s">
+        <v>24</v>
       </c>
       <c r="Q402" s="3">
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="R402" s="3">
-        <v>6.109</v>
-      </c>
-      <c r="S402" s="3">
-        <v>9.9000000000000008E-3</v>
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="R402" s="4">
+        <v>0</v>
+      </c>
+      <c r="S402" t="s">
+        <v>25</v>
       </c>
       <c r="T402">
-        <v>1086</v>
-      </c>
-      <c r="U402" s="3">
-        <v>0.98640000000000005</v>
-      </c>
-      <c r="V402" s="3">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="U402" t="s">
+        <v>25</v>
       </c>
       <c r="X402" t="s">
         <v>41</v>
@@ -29682,19 +29652,19 @@
     </row>
     <row r="403" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B403">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C403">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D403">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E403" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F403" t="s">
         <v>43</v>
@@ -29703,46 +29673,49 @@
         <v>25</v>
       </c>
       <c r="H403">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I403">
-        <v>2302</v>
+        <v>17156</v>
       </c>
       <c r="J403">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="K403">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="L403">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="M403">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N403">
         <v>0</v>
       </c>
       <c r="O403" s="2">
-        <v>2.7777777777777778E-4</v>
-      </c>
-      <c r="P403" s="2">
-        <v>8.4490740740740739E-4</v>
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="P403" t="s">
+        <v>24</v>
       </c>
       <c r="Q403" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R403" s="3">
-        <v>1.595</v>
-      </c>
-      <c r="S403" s="3">
-        <v>2.6700000000000002E-2</v>
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="S403" s="4">
+        <v>1</v>
       </c>
       <c r="T403">
-        <v>131</v>
-      </c>
-      <c r="U403" s="3">
-        <v>0.89729999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="U403" t="s">
+        <v>25</v>
+      </c>
+      <c r="V403" t="s">
+        <v>25</v>
       </c>
       <c r="X403" t="s">
         <v>41</v>
@@ -29750,19 +29723,19 @@
     </row>
     <row r="404" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B404">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C404">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D404">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E404" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F404" t="s">
         <v>43</v>
@@ -29771,49 +29744,46 @@
         <v>25</v>
       </c>
       <c r="H404">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I404">
-        <v>14762</v>
+        <v>7848</v>
       </c>
       <c r="J404">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="K404">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L404">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="M404">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N404">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O404" s="2">
-        <v>9.837962962962962E-4</v>
-      </c>
-      <c r="P404" s="2">
-        <v>1.4930555555555556E-3</v>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="P404" t="s">
+        <v>24</v>
       </c>
       <c r="Q404" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="R404" s="3">
-        <v>0.18709999999999999</v>
-      </c>
-      <c r="S404" s="3">
-        <v>0.40629999999999999</v>
+        <v>0.20280000000000001</v>
+      </c>
+      <c r="S404" s="4">
+        <v>1</v>
       </c>
       <c r="T404">
-        <v>1</v>
-      </c>
-      <c r="U404" s="3">
-        <v>5.2600000000000001E-2</v>
-      </c>
-      <c r="V404" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U404" t="s">
+        <v>25</v>
       </c>
       <c r="X404" t="s">
         <v>41</v>
@@ -29821,19 +29791,19 @@
     </row>
     <row r="405" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B405">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C405">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D405">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E405" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F405" t="s">
         <v>43</v>
@@ -29842,46 +29812,49 @@
         <v>25</v>
       </c>
       <c r="H405">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I405">
-        <v>5623</v>
+        <v>17669</v>
       </c>
       <c r="J405">
         <v>163</v>
       </c>
       <c r="K405">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L405">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="M405">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N405">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O405" s="2">
-        <v>3.9351851851851852E-4</v>
+        <v>1.2268518518518518E-3</v>
       </c>
       <c r="P405" s="2">
-        <v>4.1666666666666669E-4</v>
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="Q405" s="3">
-        <v>2.9000000000000001E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="R405" s="3">
-        <v>0.22700000000000001</v>
-      </c>
-      <c r="S405" s="3">
-        <v>0.18920000000000001</v>
+        <v>0.29449999999999998</v>
+      </c>
+      <c r="S405" s="4">
+        <v>1</v>
       </c>
       <c r="T405">
-        <v>0</v>
-      </c>
-      <c r="U405" s="4">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="U405" t="s">
+        <v>25</v>
+      </c>
+      <c r="V405" s="3">
+        <v>1</v>
       </c>
       <c r="X405" t="s">
         <v>41</v>
@@ -29889,19 +29862,19 @@
     </row>
     <row r="406" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B406">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C406">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D406">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E406" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F406" t="s">
         <v>43</v>
@@ -29910,49 +29883,46 @@
         <v>25</v>
       </c>
       <c r="H406">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I406">
-        <v>16376</v>
+        <v>6190</v>
       </c>
       <c r="J406">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="K406">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="L406">
         <v>30</v>
       </c>
       <c r="M406">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N406">
         <v>0</v>
       </c>
       <c r="O406" s="2">
-        <v>1.1921296296296296E-3</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="P406" s="2">
-        <v>3.2407407407407406E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="Q406" s="3">
-        <v>9.5999999999999992E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R406" s="3">
-        <v>0.36309999999999998</v>
-      </c>
-      <c r="S406" s="3">
-        <v>0.52629999999999999</v>
+        <v>0.3226</v>
+      </c>
+      <c r="S406" s="4">
+        <v>1</v>
       </c>
       <c r="T406">
-        <v>16</v>
-      </c>
-      <c r="U406" s="3">
-        <v>0.59260000000000002</v>
-      </c>
-      <c r="V406" s="3">
-        <v>1</v>
+        <v>-14</v>
+      </c>
+      <c r="U406" t="s">
+        <v>25</v>
       </c>
       <c r="X406" t="s">
         <v>41</v>
@@ -29960,19 +29930,19 @@
     </row>
     <row r="407" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B407">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C407">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D407">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E407" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F407" t="s">
         <v>43</v>
@@ -29981,46 +29951,49 @@
         <v>25</v>
       </c>
       <c r="H407">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I407">
-        <v>8943</v>
+        <v>21673</v>
       </c>
       <c r="J407">
-        <v>253</v>
+        <v>165</v>
       </c>
       <c r="K407">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="L407">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="M407">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N407">
         <v>0</v>
       </c>
       <c r="O407" s="2">
-        <v>4.0509259259259258E-4</v>
+        <v>1.4699074074074074E-3</v>
       </c>
       <c r="P407" s="2">
-        <v>4.5138888888888887E-4</v>
+        <v>1.1921296296296296E-3</v>
       </c>
       <c r="Q407" s="3">
-        <v>2.8299999999999999E-2</v>
+        <v>7.6E-3</v>
       </c>
       <c r="R407" s="3">
-        <v>0.2964</v>
-      </c>
-      <c r="S407" s="3">
-        <v>0.33329999999999999</v>
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="S407" s="4">
+        <v>1</v>
       </c>
       <c r="T407">
-        <v>10</v>
-      </c>
-      <c r="U407" s="4">
-        <v>0.2</v>
+        <v>-25</v>
+      </c>
+      <c r="U407" t="s">
+        <v>25</v>
+      </c>
+      <c r="V407" s="3">
+        <v>1</v>
       </c>
       <c r="X407" t="s">
         <v>41</v>
@@ -30028,19 +30001,19 @@
     </row>
     <row r="408" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B408">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C408">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D408">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E408" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F408" t="s">
         <v>43</v>
@@ -30049,49 +30022,46 @@
         <v>25</v>
       </c>
       <c r="H408">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I408">
-        <v>17306</v>
+        <v>2538</v>
       </c>
       <c r="J408">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="K408">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="L408">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M408">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N408">
         <v>0</v>
       </c>
       <c r="O408" s="2">
-        <v>1.7013888888888888E-3</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="P408" s="2">
-        <v>7.291666666666667E-4</v>
+        <v>4.861111111111111E-4</v>
       </c>
       <c r="Q408" s="3">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="R408" s="3">
-        <v>0.30769999999999997</v>
-      </c>
-      <c r="S408" s="3">
-        <v>0.52780000000000005</v>
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="R408" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="S408" s="4">
+        <v>1</v>
       </c>
       <c r="T408">
-        <v>6</v>
-      </c>
-      <c r="U408" s="3">
-        <v>0.35289999999999999</v>
-      </c>
-      <c r="V408" s="3">
-        <v>1</v>
+        <v>-8</v>
+      </c>
+      <c r="U408" t="s">
+        <v>25</v>
       </c>
       <c r="X408" t="s">
         <v>41</v>
@@ -30099,19 +30069,19 @@
     </row>
     <row r="409" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B409">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C409">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D409">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E409" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F409" t="s">
         <v>43</v>
@@ -30120,46 +30090,49 @@
         <v>25</v>
       </c>
       <c r="H409">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I409">
-        <v>6585</v>
+        <v>17931</v>
       </c>
       <c r="J409">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K409">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L409">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M409">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O409" s="2">
-        <v>4.7453703703703704E-4</v>
+        <v>1.4120370370370369E-3</v>
       </c>
       <c r="P409" s="2">
-        <v>6.134259259259259E-4</v>
+        <v>1.4120370370370369E-3</v>
       </c>
       <c r="Q409" s="3">
-        <v>2.41E-2</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="R409" s="3">
-        <v>0.24529999999999999</v>
-      </c>
-      <c r="S409" s="3">
-        <v>0.28210000000000002</v>
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="S409" s="4">
+        <v>1</v>
       </c>
       <c r="T409">
-        <v>15</v>
-      </c>
-      <c r="U409" s="3">
-        <v>0.53569999999999995</v>
+        <v>-15</v>
+      </c>
+      <c r="U409" t="s">
+        <v>25</v>
+      </c>
+      <c r="V409" s="3">
+        <v>1</v>
       </c>
       <c r="X409" t="s">
         <v>41</v>
@@ -30167,69 +30140,66 @@
     </row>
     <row r="410" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B410">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C410">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D410">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E410" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F410" t="s">
         <v>43</v>
       </c>
       <c r="G410">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H410">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I410">
-        <v>133</v>
+        <v>2818</v>
       </c>
       <c r="J410">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="K410">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L410">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M410">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N410">
         <v>0</v>
       </c>
-      <c r="O410" t="s">
-        <v>24</v>
-      </c>
-      <c r="P410" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q410" s="4">
-        <v>0</v>
-      </c>
-      <c r="R410" t="s">
-        <v>25</v>
-      </c>
-      <c r="S410" t="s">
-        <v>25</v>
+      <c r="O410" s="2">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P410" s="2">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="Q410" s="3">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="R410" s="3">
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="S410" s="4">
+        <v>1</v>
       </c>
       <c r="T410">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="U410" t="s">
-        <v>25</v>
-      </c>
-      <c r="V410" t="s">
         <v>25</v>
       </c>
       <c r="X410" t="s">
@@ -30238,67 +30208,70 @@
     </row>
     <row r="411" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B411">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C411">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D411">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E411" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F411" t="s">
         <v>43</v>
       </c>
       <c r="G411">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H411">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I411">
-        <v>32</v>
+        <v>31421</v>
       </c>
       <c r="J411">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="K411">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L411">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M411">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N411">
         <v>0</v>
       </c>
       <c r="O411" s="2">
-        <v>3.7037037037037035E-4</v>
-      </c>
-      <c r="P411" t="s">
-        <v>24</v>
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="P411" s="2">
+        <v>1.2152777777777778E-3</v>
       </c>
       <c r="Q411" s="3">
-        <v>3.1300000000000001E-2</v>
-      </c>
-      <c r="R411" s="4">
-        <v>0</v>
-      </c>
-      <c r="S411" t="s">
-        <v>25</v>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="R411" s="3">
+        <v>0.18659999999999999</v>
+      </c>
+      <c r="S411" s="4">
+        <v>1</v>
       </c>
       <c r="T411">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="U411" t="s">
         <v>25</v>
+      </c>
+      <c r="V411" s="3">
+        <v>1</v>
       </c>
       <c r="X411" t="s">
         <v>41</v>
@@ -30309,16 +30282,16 @@
         <v>46184</v>
       </c>
       <c r="B412">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C412">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D412">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E412" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F412" t="s">
         <v>43</v>
@@ -30327,48 +30300,45 @@
         <v>25</v>
       </c>
       <c r="H412">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I412">
-        <v>17156</v>
+        <v>1295</v>
       </c>
       <c r="J412">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="K412">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L412">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M412">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N412">
         <v>0</v>
       </c>
       <c r="O412" s="2">
-        <v>1.4236111111111112E-3</v>
-      </c>
-      <c r="P412" t="s">
-        <v>24</v>
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P412" s="2">
+        <v>7.8703703703703705E-4</v>
       </c>
       <c r="Q412" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>3.9399999999999998E-2</v>
       </c>
       <c r="R412" s="3">
-        <v>0.28989999999999999</v>
+        <v>0.39219999999999999</v>
       </c>
       <c r="S412" s="4">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="T412">
-        <v>22</v>
-      </c>
-      <c r="U412" s="4">
-        <v>1</v>
-      </c>
-      <c r="V412" t="s">
+        <v>-12</v>
+      </c>
+      <c r="U412" t="s">
         <v>25</v>
       </c>
       <c r="X412" t="s">
@@ -30380,16 +30350,16 @@
         <v>46184</v>
       </c>
       <c r="B413">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C413">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D413">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E413" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F413" t="s">
         <v>43</v>
@@ -30398,45 +30368,48 @@
         <v>25</v>
       </c>
       <c r="H413">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I413">
-        <v>7848</v>
+        <v>32181</v>
       </c>
       <c r="J413">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="K413">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L413">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="M413">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N413">
         <v>0</v>
       </c>
       <c r="O413" s="2">
-        <v>6.2500000000000001E-4</v>
-      </c>
-      <c r="P413" t="s">
-        <v>24</v>
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="P413" s="2">
+        <v>1.5740740740740741E-3</v>
       </c>
       <c r="Q413" s="3">
-        <v>1.8200000000000001E-2</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="R413" s="3">
-        <v>0.2238</v>
-      </c>
-      <c r="S413" s="3">
-        <v>0.28129999999999999</v>
+        <v>0.1938</v>
+      </c>
+      <c r="S413" s="4">
+        <v>1</v>
       </c>
       <c r="T413">
-        <v>23</v>
-      </c>
-      <c r="U413" s="4">
+        <v>-21</v>
+      </c>
+      <c r="U413" t="s">
+        <v>25</v>
+      </c>
+      <c r="V413" s="3">
         <v>1</v>
       </c>
       <c r="X413" t="s">
@@ -30448,7 +30421,7 @@
         <v>46184</v>
       </c>
       <c r="B414">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C414">
         <v>81</v>
@@ -30466,46 +30439,46 @@
         <v>25</v>
       </c>
       <c r="H414">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I414">
-        <v>17669</v>
+        <v>12598</v>
       </c>
       <c r="J414">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="K414">
-        <v>1068</v>
+        <v>18</v>
       </c>
       <c r="L414">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M414">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N414">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O414" s="2">
-        <v>1.2268518518518518E-3</v>
+        <v>1.9560185185185184E-3</v>
       </c>
       <c r="P414" s="2">
-        <v>1.5740740740740741E-3</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="Q414" s="3">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="R414" s="3">
-        <v>6.5519999999999996</v>
-      </c>
-      <c r="S414" s="3">
-        <v>2.9000000000000001E-2</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="R414" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="S414" s="4">
+        <v>1</v>
       </c>
       <c r="T414">
-        <v>1017</v>
-      </c>
-      <c r="U414" s="3">
-        <v>0.98070000000000002</v>
+        <v>-7</v>
+      </c>
+      <c r="U414" t="s">
+        <v>25</v>
       </c>
       <c r="V414" s="3">
         <v>1</v>
@@ -30519,16 +30492,16 @@
         <v>46184</v>
       </c>
       <c r="B415">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C415">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D415">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E415" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F415" t="s">
         <v>43</v>
@@ -30537,46 +30510,49 @@
         <v>25</v>
       </c>
       <c r="H415">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I415">
-        <v>6190</v>
+        <v>19843</v>
       </c>
       <c r="J415">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="K415">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="L415">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="M415">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N415">
         <v>0</v>
       </c>
       <c r="O415" s="2">
-        <v>7.5231481481481482E-4</v>
+        <v>1.5625000000000001E-3</v>
       </c>
       <c r="P415" s="2">
-        <v>2.7777777777777778E-4</v>
+        <v>9.3749999999999997E-4</v>
       </c>
       <c r="Q415" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="R415" s="3">
-        <v>3.01</v>
-      </c>
-      <c r="S415" s="3">
-        <v>3.2099999999999997E-2</v>
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="S415" s="4">
+        <v>1</v>
       </c>
       <c r="T415">
-        <v>257</v>
-      </c>
-      <c r="U415" s="3">
-        <v>0.94830000000000003</v>
+        <v>-10</v>
+      </c>
+      <c r="U415" t="s">
+        <v>25</v>
+      </c>
+      <c r="V415" s="3">
+        <v>1</v>
       </c>
       <c r="X415" t="s">
         <v>41</v>
@@ -30587,7 +30563,7 @@
         <v>46184</v>
       </c>
       <c r="B416">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C416">
         <v>81</v>
@@ -30608,43 +30584,43 @@
         <v>8</v>
       </c>
       <c r="I416">
-        <v>21673</v>
+        <v>31658</v>
       </c>
       <c r="J416">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="K416">
-        <v>1685</v>
+        <v>72</v>
       </c>
       <c r="L416">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="M416">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N416">
         <v>0</v>
       </c>
       <c r="O416" s="2">
-        <v>1.4699074074074074E-3</v>
+        <v>1.4930555555555556E-3</v>
       </c>
       <c r="P416" s="2">
-        <v>1.1921296296296296E-3</v>
+        <v>1.0648148148148149E-3</v>
       </c>
       <c r="Q416" s="3">
         <v>7.6E-3</v>
       </c>
-      <c r="R416" s="3">
-        <v>10.210000000000001</v>
-      </c>
-      <c r="S416" s="3">
-        <v>1.3599999999999999E-2</v>
+      <c r="R416" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="S416" s="4">
+        <v>1</v>
       </c>
       <c r="T416">
-        <v>1637</v>
-      </c>
-      <c r="U416" s="3">
-        <v>0.98499999999999999</v>
+        <v>-16</v>
+      </c>
+      <c r="U416" t="s">
+        <v>25</v>
       </c>
       <c r="V416" s="3">
         <v>1</v>
@@ -30658,16 +30634,16 @@
         <v>46184</v>
       </c>
       <c r="B417">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C417">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D417">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E417" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F417" t="s">
         <v>43</v>
@@ -30676,46 +30652,49 @@
         <v>25</v>
       </c>
       <c r="H417">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I417">
-        <v>2538</v>
+        <v>28923</v>
       </c>
       <c r="J417">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="K417">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="L417">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="M417">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N417">
         <v>0</v>
       </c>
       <c r="O417" s="2">
-        <v>3.8194444444444446E-4</v>
+        <v>2.3379629629629631E-3</v>
       </c>
       <c r="P417" s="2">
-        <v>4.861111111111111E-4</v>
+        <v>1.5856481481481481E-3</v>
       </c>
       <c r="Q417" s="3">
-        <v>2.9600000000000001E-2</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="R417" s="3">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="S417" s="3">
-        <v>5.2600000000000001E-2</v>
+        <v>0.29289999999999999</v>
+      </c>
+      <c r="S417" s="4">
+        <v>1</v>
       </c>
       <c r="T417">
-        <v>64</v>
-      </c>
-      <c r="U417" s="3">
-        <v>0.88890000000000002</v>
+        <v>-10</v>
+      </c>
+      <c r="U417" t="s">
+        <v>25</v>
+      </c>
+      <c r="V417" s="3">
+        <v>0.92310000000000003</v>
       </c>
       <c r="X417" t="s">
         <v>41</v>
@@ -30726,7 +30705,7 @@
         <v>46184</v>
       </c>
       <c r="B418">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C418">
         <v>81</v>
@@ -30741,52 +30720,52 @@
         <v>43</v>
       </c>
       <c r="G418">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H418">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I418">
-        <v>17931</v>
+        <v>285</v>
       </c>
       <c r="J418">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="K418">
-        <v>2061</v>
+        <v>0</v>
       </c>
       <c r="L418">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M418">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N418">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O418" s="2">
-        <v>1.4120370370370369E-3</v>
-      </c>
-      <c r="P418" s="2">
-        <v>1.4120370370370369E-3</v>
+        <v>1.6435185185185185E-3</v>
+      </c>
+      <c r="P418" t="s">
+        <v>24</v>
       </c>
       <c r="Q418" s="3">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="R418" s="3">
-        <v>14.61</v>
-      </c>
-      <c r="S418" s="3">
-        <v>1.3599999999999999E-2</v>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R418" s="4">
+        <v>0</v>
+      </c>
+      <c r="S418" t="s">
+        <v>25</v>
       </c>
       <c r="T418">
-        <v>2018</v>
-      </c>
-      <c r="U418" s="3">
-        <v>0.99260000000000004</v>
-      </c>
-      <c r="V418" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U418" t="s">
+        <v>25</v>
+      </c>
+      <c r="V418" t="s">
+        <v>25</v>
       </c>
       <c r="X418" t="s">
         <v>41</v>
@@ -30794,19 +30773,19 @@
     </row>
     <row r="419" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B419">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C419">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D419">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E419" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F419" t="s">
         <v>43</v>
@@ -30815,46 +30794,49 @@
         <v>25</v>
       </c>
       <c r="H419">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I419">
-        <v>2818</v>
+        <v>18853</v>
       </c>
       <c r="J419">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K419">
-        <v>231</v>
+        <v>28</v>
       </c>
       <c r="L419">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M419">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N419">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O419" s="2">
-        <v>2.6620370370370372E-4</v>
+        <v>1.8634259259259259E-3</v>
       </c>
       <c r="P419" s="2">
-        <v>1.5162037037037036E-3</v>
+        <v>1.4467592592592592E-3</v>
       </c>
       <c r="Q419" s="3">
-        <v>4.2200000000000001E-2</v>
-      </c>
-      <c r="R419" s="3">
-        <v>1.9410000000000001</v>
-      </c>
-      <c r="S419" s="3">
-        <v>1.7299999999999999E-2</v>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="R419" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="S419" s="4">
+        <v>1</v>
       </c>
       <c r="T419">
-        <v>210</v>
-      </c>
-      <c r="U419" s="3">
-        <v>0.92510000000000003</v>
+        <v>-7</v>
+      </c>
+      <c r="U419" t="s">
+        <v>25</v>
+      </c>
+      <c r="V419" s="3">
+        <v>1</v>
       </c>
       <c r="X419" t="s">
         <v>41</v>
@@ -30862,10 +30844,10 @@
     </row>
     <row r="420" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B420">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C420">
         <v>81</v>
@@ -30883,46 +30865,46 @@
         <v>25</v>
       </c>
       <c r="H420">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I420">
-        <v>31421</v>
+        <v>31100</v>
       </c>
       <c r="J420">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="K420">
-        <v>4079</v>
+        <v>70</v>
       </c>
       <c r="L420">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="M420">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N420">
         <v>0</v>
       </c>
       <c r="O420" s="2">
-        <v>1.6666666666666668E-3</v>
+        <v>1.4699074074074074E-3</v>
       </c>
       <c r="P420" s="2">
-        <v>1.2152777777777778E-3</v>
+        <v>6.7129629629629625E-4</v>
       </c>
       <c r="Q420" s="3">
-        <v>6.7000000000000002E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="R420" s="3">
-        <v>19.510000000000002</v>
-      </c>
-      <c r="S420" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>0.29909999999999998</v>
+      </c>
+      <c r="S420" s="4">
+        <v>1</v>
       </c>
       <c r="T420">
-        <v>4037</v>
-      </c>
-      <c r="U420" s="3">
-        <v>0.99609999999999999</v>
+        <v>-14</v>
+      </c>
+      <c r="U420" t="s">
+        <v>25</v>
       </c>
       <c r="V420" s="3">
         <v>1</v>
@@ -30933,19 +30915,19 @@
     </row>
     <row r="421" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B421">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C421">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D421">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E421" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F421" t="s">
         <v>43</v>
@@ -30954,46 +30936,49 @@
         <v>25</v>
       </c>
       <c r="H421">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I421">
-        <v>1295</v>
+        <v>29093</v>
       </c>
       <c r="J421">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="K421">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="L421">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="M421">
         <v>12</v>
       </c>
       <c r="N421">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O421" s="2">
-        <v>2.7777777777777778E-4</v>
+        <v>2.3611111111111111E-3</v>
       </c>
       <c r="P421" s="2">
-        <v>7.8703703703703705E-4</v>
+        <v>1.2268518518518518E-3</v>
       </c>
       <c r="Q421" s="3">
-        <v>3.9399999999999998E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="R421" s="3">
-        <v>4.0780000000000003</v>
-      </c>
-      <c r="S421" s="3">
-        <v>1.44E-2</v>
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="S421" s="4">
+        <v>1</v>
       </c>
       <c r="T421">
-        <v>193</v>
-      </c>
-      <c r="U421" s="3">
-        <v>0.9415</v>
+        <v>-12</v>
+      </c>
+      <c r="U421" t="s">
+        <v>25</v>
+      </c>
+      <c r="V421" s="3">
+        <v>1</v>
       </c>
       <c r="X421" t="s">
         <v>41</v>
@@ -31001,10 +30986,10 @@
     </row>
     <row r="422" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B422">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C422">
         <v>81</v>
@@ -31022,46 +31007,46 @@
         <v>25</v>
       </c>
       <c r="H422">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I422">
-        <v>32181</v>
+        <v>21877</v>
       </c>
       <c r="J422">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="K422">
-        <v>4284</v>
+        <v>30</v>
       </c>
       <c r="L422">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M422">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N422">
         <v>0</v>
       </c>
       <c r="O422" s="2">
-        <v>1.5393518518518519E-3</v>
+        <v>2.2916666666666667E-3</v>
       </c>
       <c r="P422" s="2">
-        <v>1.5740740740740741E-3</v>
+        <v>7.6388888888888893E-4</v>
       </c>
       <c r="Q422" s="3">
-        <v>7.1000000000000004E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="R422" s="3">
-        <v>18.87</v>
-      </c>
-      <c r="S422" s="3">
-        <v>6.1000000000000004E-3</v>
+        <v>0.28039999999999998</v>
+      </c>
+      <c r="S422" s="4">
+        <v>1</v>
       </c>
       <c r="T422">
-        <v>4237</v>
-      </c>
-      <c r="U422" s="3">
-        <v>0.99509999999999998</v>
+        <v>-16</v>
+      </c>
+      <c r="U422" t="s">
+        <v>25</v>
       </c>
       <c r="V422" s="3">
         <v>1</v>
@@ -31072,10 +31057,10 @@
     </row>
     <row r="423" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B423">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C423">
         <v>81</v>
@@ -31093,19 +31078,19 @@
         <v>25</v>
       </c>
       <c r="H423">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I423">
-        <v>12598</v>
+        <v>14372</v>
       </c>
       <c r="J423">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K423">
-        <v>1575</v>
+        <v>22</v>
       </c>
       <c r="L423">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M423">
         <v>7</v>
@@ -31114,25 +31099,25 @@
         <v>0</v>
       </c>
       <c r="O423" s="2">
-        <v>1.9560185185185184E-3</v>
+        <v>1.9444444444444444E-3</v>
       </c>
       <c r="P423" s="2">
-        <v>2.0833333333333335E-4</v>
+        <v>1.4930555555555556E-3</v>
       </c>
       <c r="Q423" s="3">
-        <v>5.7000000000000002E-3</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R423" s="3">
-        <v>21.87</v>
-      </c>
-      <c r="S423" s="3">
-        <v>8.3000000000000001E-3</v>
+        <v>0.25879999999999997</v>
+      </c>
+      <c r="S423" s="4">
+        <v>1</v>
       </c>
       <c r="T423">
-        <v>1555</v>
-      </c>
-      <c r="U423" s="3">
-        <v>0.99550000000000005</v>
+        <v>-7</v>
+      </c>
+      <c r="U423" t="s">
+        <v>25</v>
       </c>
       <c r="V423" s="3">
         <v>1</v>
@@ -31143,10 +31128,10 @@
     </row>
     <row r="424" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B424">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C424">
         <v>81</v>
@@ -31164,46 +31149,46 @@
         <v>25</v>
       </c>
       <c r="H424">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I424">
-        <v>19843</v>
+        <v>16434</v>
       </c>
       <c r="J424">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K424">
-        <v>1634</v>
+        <v>18</v>
       </c>
       <c r="L424">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M424">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N424">
         <v>0</v>
       </c>
       <c r="O424" s="2">
-        <v>1.5625000000000001E-3</v>
+        <v>1.4814814814814814E-3</v>
       </c>
       <c r="P424" s="2">
-        <v>9.3749999999999997E-4</v>
+        <v>8.1018518518518516E-4</v>
       </c>
       <c r="Q424" s="3">
-        <v>7.1000000000000004E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="R424" s="3">
-        <v>11.67</v>
-      </c>
-      <c r="S424" s="3">
-        <v>9.7999999999999997E-3</v>
+        <v>0.1429</v>
+      </c>
+      <c r="S424" s="4">
+        <v>1</v>
       </c>
       <c r="T424">
-        <v>1608</v>
-      </c>
-      <c r="U424" s="3">
-        <v>0.99380000000000002</v>
+        <v>-5</v>
+      </c>
+      <c r="U424" t="s">
+        <v>25</v>
       </c>
       <c r="V424" s="3">
         <v>1</v>
@@ -31214,10 +31199,10 @@
     </row>
     <row r="425" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B425">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C425">
         <v>81</v>
@@ -31235,46 +31220,46 @@
         <v>25</v>
       </c>
       <c r="H425">
+        <v>3</v>
+      </c>
+      <c r="I425">
+        <v>16782</v>
+      </c>
+      <c r="J425">
+        <v>115</v>
+      </c>
+      <c r="K425">
+        <v>18</v>
+      </c>
+      <c r="L425">
+        <v>18</v>
+      </c>
+      <c r="M425">
         <v>8</v>
       </c>
-      <c r="I425">
-        <v>31658</v>
-      </c>
-      <c r="J425">
-        <v>240</v>
-      </c>
-      <c r="K425">
-        <v>1300</v>
-      </c>
-      <c r="L425">
-        <v>57</v>
-      </c>
-      <c r="M425">
-        <v>16</v>
-      </c>
       <c r="N425">
         <v>0</v>
       </c>
       <c r="O425" s="2">
-        <v>1.4930555555555556E-3</v>
+        <v>1.6666666666666668E-3</v>
       </c>
       <c r="P425" s="2">
-        <v>1.0648148148148149E-3</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="Q425" s="3">
-        <v>7.6E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="R425" s="3">
-        <v>5.4160000000000004</v>
-      </c>
-      <c r="S425" s="3">
-        <v>4.3799999999999999E-2</v>
+        <v>0.1565</v>
+      </c>
+      <c r="S425" s="4">
+        <v>1</v>
       </c>
       <c r="T425">
-        <v>1227</v>
-      </c>
-      <c r="U425" s="3">
-        <v>0.98709999999999998</v>
+        <v>-8</v>
+      </c>
+      <c r="U425" t="s">
+        <v>25</v>
       </c>
       <c r="V425" s="3">
         <v>1</v>
@@ -31285,10 +31270,10 @@
     </row>
     <row r="426" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B426">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C426">
         <v>81</v>
@@ -31309,46 +31294,46 @@
         <v>5</v>
       </c>
       <c r="I426">
-        <v>28923</v>
+        <v>15999</v>
       </c>
       <c r="J426">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="K426">
-        <v>1897</v>
+        <v>17</v>
       </c>
       <c r="L426">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="M426">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N426">
         <v>0</v>
       </c>
       <c r="O426" s="2">
-        <v>2.3379629629629631E-3</v>
+        <v>1.4930555555555556E-3</v>
       </c>
       <c r="P426" s="2">
-        <v>1.5856481481481481E-3</v>
+        <v>3.8194444444444446E-4</v>
       </c>
       <c r="Q426" s="3">
-        <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="R426" s="4">
-        <v>13.55</v>
-      </c>
-      <c r="S426" s="3">
-        <v>1.6299999999999999E-2</v>
+        <v>7.6E-3</v>
+      </c>
+      <c r="R426" s="3">
+        <v>0.14050000000000001</v>
+      </c>
+      <c r="S426" s="4">
+        <v>1</v>
       </c>
       <c r="T426">
-        <v>1856</v>
-      </c>
-      <c r="U426" s="3">
-        <v>0.99460000000000004</v>
+        <v>-6</v>
+      </c>
+      <c r="U426" t="s">
+        <v>25</v>
       </c>
       <c r="V426" s="3">
-        <v>0.92310000000000003</v>
+        <v>1</v>
       </c>
       <c r="X426" t="s">
         <v>41</v>
@@ -31356,10 +31341,10 @@
     </row>
     <row r="427" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B427">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C427">
         <v>81</v>
@@ -31374,52 +31359,52 @@
         <v>43</v>
       </c>
       <c r="G427">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H427">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I427">
-        <v>285</v>
+        <v>22246</v>
       </c>
       <c r="J427">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="K427">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L427">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M427">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N427">
         <v>0</v>
       </c>
       <c r="O427" s="2">
-        <v>1.6435185185185185E-3</v>
-      </c>
-      <c r="P427" t="s">
-        <v>24</v>
+        <v>1.2731481481481483E-3</v>
+      </c>
+      <c r="P427" s="2">
+        <v>1.0995370370370371E-3</v>
       </c>
       <c r="Q427" s="3">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="R427" s="4">
-        <v>36.5</v>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R427" s="3">
+        <v>0.29499999999999998</v>
       </c>
       <c r="S427" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T427">
-        <v>73</v>
-      </c>
-      <c r="U427" s="4">
-        <v>1</v>
-      </c>
-      <c r="V427" t="s">
-        <v>25</v>
+        <v>-10</v>
+      </c>
+      <c r="U427" t="s">
+        <v>25</v>
+      </c>
+      <c r="V427" s="3">
+        <v>1</v>
       </c>
       <c r="X427" t="s">
         <v>41</v>
@@ -31430,7 +31415,7 @@
         <v>46185</v>
       </c>
       <c r="B428">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C428">
         <v>81</v>
@@ -31445,52 +31430,52 @@
         <v>43</v>
       </c>
       <c r="G428">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H428">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I428">
-        <v>18853</v>
+        <v>103</v>
       </c>
       <c r="J428">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="K428">
-        <v>2143</v>
+        <v>0</v>
       </c>
       <c r="L428">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M428">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O428" s="2">
-        <v>1.8634259259259259E-3</v>
-      </c>
-      <c r="P428" s="2">
-        <v>1.4467592592592592E-3</v>
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="P428" t="s">
+        <v>24</v>
       </c>
       <c r="Q428" s="3">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="R428" s="3">
-        <v>19.13</v>
-      </c>
-      <c r="S428" s="3">
-        <v>9.2999999999999992E-3</v>
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="R428" s="4">
+        <v>0</v>
+      </c>
+      <c r="S428" t="s">
+        <v>25</v>
       </c>
       <c r="T428">
-        <v>2116</v>
-      </c>
-      <c r="U428" s="3">
-        <v>0.99670000000000003</v>
-      </c>
-      <c r="V428" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U428" t="s">
+        <v>25</v>
+      </c>
+      <c r="V428" t="s">
+        <v>25</v>
       </c>
       <c r="X428" t="s">
         <v>41</v>
@@ -31498,7 +31483,7 @@
     </row>
     <row r="429" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B429">
         <v>10</v>
@@ -31519,49 +31504,52 @@
         <v>25</v>
       </c>
       <c r="H429">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I429">
-        <v>31100</v>
+        <v>11497</v>
       </c>
       <c r="J429">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="K429">
-        <v>3917</v>
+        <v>50</v>
       </c>
       <c r="L429">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M429">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N429">
         <v>0</v>
       </c>
       <c r="O429" s="2">
-        <v>1.4699074074074074E-3</v>
+        <v>9.9537037037037042E-4</v>
       </c>
       <c r="P429" s="2">
-        <v>6.7129629629629625E-4</v>
+        <v>2.3379629629629631E-3</v>
       </c>
       <c r="Q429" s="3">
-        <v>7.4999999999999997E-3</v>
+        <v>1.15E-2</v>
       </c>
       <c r="R429" s="3">
-        <v>16.73</v>
-      </c>
-      <c r="S429" s="3">
-        <v>1.5100000000000001E-2</v>
+        <v>0.37880000000000003</v>
+      </c>
+      <c r="S429" s="4">
+        <v>1</v>
       </c>
       <c r="T429">
-        <v>3844</v>
-      </c>
-      <c r="U429" s="3">
-        <v>0.99639999999999995</v>
+        <v>-13</v>
+      </c>
+      <c r="U429" t="s">
+        <v>25</v>
       </c>
       <c r="V429" s="3">
         <v>1</v>
+      </c>
+      <c r="W429">
+        <v>3.6659999999999999</v>
       </c>
       <c r="X429" t="s">
         <v>41</v>
@@ -31569,7 +31557,7 @@
     </row>
     <row r="430" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B430">
         <v>11</v>
@@ -31593,46 +31581,49 @@
         <v>8</v>
       </c>
       <c r="I430">
-        <v>29093</v>
+        <v>30692</v>
       </c>
       <c r="J430">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="K430">
-        <v>3319</v>
+        <v>82</v>
       </c>
       <c r="L430">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="M430">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="N430">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O430" s="2">
-        <v>2.3611111111111111E-3</v>
+        <v>1.3541666666666667E-3</v>
       </c>
       <c r="P430" s="2">
-        <v>1.2268518518518518E-3</v>
+        <v>1.8055555555555555E-3</v>
       </c>
       <c r="Q430" s="3">
-        <v>4.7000000000000002E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="R430" s="3">
-        <v>24.05</v>
-      </c>
-      <c r="S430" s="3">
-        <v>8.6999999999999994E-3</v>
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="S430" s="4">
+        <v>1</v>
       </c>
       <c r="T430">
-        <v>3278</v>
-      </c>
-      <c r="U430" s="3">
-        <v>0.99639999999999995</v>
+        <v>-30</v>
+      </c>
+      <c r="U430" t="s">
+        <v>25</v>
       </c>
       <c r="V430" s="3">
-        <v>1</v>
+        <v>0.9677</v>
+      </c>
+      <c r="W430">
+        <v>34.128</v>
       </c>
       <c r="X430" t="s">
         <v>41</v>
@@ -31640,7 +31631,7 @@
     </row>
     <row r="431" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B431">
         <v>12</v>
@@ -31661,49 +31652,52 @@
         <v>25</v>
       </c>
       <c r="H431">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I431">
-        <v>21877</v>
+        <v>33207</v>
       </c>
       <c r="J431">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="K431">
-        <v>1495</v>
+        <v>60</v>
       </c>
       <c r="L431">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="M431">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="N431">
         <v>0</v>
       </c>
       <c r="O431" s="2">
-        <v>2.2916666666666667E-3</v>
+        <v>1.5856481481481481E-3</v>
       </c>
       <c r="P431" s="2">
-        <v>7.6388888888888893E-4</v>
+        <v>2.8935185185185184E-4</v>
       </c>
       <c r="Q431" s="3">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="R431" s="3">
-        <v>13.97</v>
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R431" s="4">
+        <v>0.25</v>
       </c>
       <c r="S431" s="4">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T431">
-        <v>1464</v>
-      </c>
-      <c r="U431" s="3">
-        <v>0.98919999999999997</v>
+        <v>-1</v>
+      </c>
+      <c r="U431" t="s">
+        <v>25</v>
       </c>
       <c r="V431" s="3">
         <v>1</v>
+      </c>
+      <c r="W431">
+        <v>22.643999999999998</v>
       </c>
       <c r="X431" t="s">
         <v>41</v>
@@ -31711,7 +31705,7 @@
     </row>
     <row r="432" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B432">
         <v>13</v>
@@ -31729,52 +31723,55 @@
         <v>43</v>
       </c>
       <c r="G432">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H432">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I432">
-        <v>14372</v>
+        <v>23624</v>
       </c>
       <c r="J432">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="K432">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L432">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M432">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N432">
         <v>0</v>
       </c>
       <c r="O432" s="2">
-        <v>1.9444444444444444E-3</v>
-      </c>
-      <c r="P432" s="2">
-        <v>1.4930555555555556E-3</v>
+        <v>1.2268518518518518E-3</v>
+      </c>
+      <c r="P432" t="s">
+        <v>24</v>
       </c>
       <c r="Q432" s="3">
-        <v>5.8999999999999999E-3</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="R432" s="3">
-        <v>0.32940000000000003</v>
-      </c>
-      <c r="S432" s="3">
-        <v>0.57140000000000002</v>
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="S432" s="4">
+        <v>1</v>
       </c>
       <c r="T432">
-        <v>5</v>
-      </c>
-      <c r="U432" s="3">
-        <v>0.41670000000000001</v>
-      </c>
-      <c r="V432" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U432" t="s">
+        <v>25</v>
+      </c>
+      <c r="V432" t="s">
+        <v>25</v>
+      </c>
+      <c r="W432">
+        <v>26.43</v>
       </c>
       <c r="X432" t="s">
         <v>41</v>
@@ -31782,7 +31779,7 @@
     </row>
     <row r="433" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B433">
         <v>14</v>
@@ -31803,49 +31800,52 @@
         <v>25</v>
       </c>
       <c r="H433">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I433">
-        <v>16434</v>
+        <v>22591</v>
       </c>
       <c r="J433">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="K433">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L433">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M433">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N433">
         <v>0</v>
       </c>
       <c r="O433" s="2">
-        <v>1.4814814814814814E-3</v>
-      </c>
-      <c r="P433" s="2">
-        <v>8.1018518518518516E-4</v>
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="P433" t="s">
+        <v>24</v>
       </c>
       <c r="Q433" s="3">
-        <v>7.7000000000000002E-3</v>
+        <v>1.06E-2</v>
       </c>
       <c r="R433" s="3">
-        <v>0.23019999999999999</v>
-      </c>
-      <c r="S433" s="3">
-        <v>0.48280000000000001</v>
+        <v>0.1172</v>
+      </c>
+      <c r="S433" s="4">
+        <v>1</v>
       </c>
       <c r="T433">
-        <v>10</v>
-      </c>
-      <c r="U433" s="3">
-        <v>0.66669999999999996</v>
-      </c>
-      <c r="V433" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U433" t="s">
+        <v>25</v>
+      </c>
+      <c r="V433" t="s">
+        <v>25</v>
+      </c>
+      <c r="W433">
+        <v>24.654</v>
       </c>
       <c r="X433" t="s">
         <v>41</v>
@@ -31853,7 +31853,7 @@
     </row>
     <row r="434" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B434">
         <v>15</v>
@@ -31874,49 +31874,52 @@
         <v>25</v>
       </c>
       <c r="H434">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I434">
-        <v>16782</v>
+        <v>21702</v>
       </c>
       <c r="J434">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="K434">
-        <v>1105</v>
+        <v>51</v>
       </c>
       <c r="L434">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="M434">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N434">
         <v>0</v>
       </c>
       <c r="O434" s="2">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="P434" s="2">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="Q434" s="3">
-        <v>6.8999999999999999E-3</v>
+        <v>1.1458333333333333E-3</v>
+      </c>
+      <c r="P434" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q434" s="4">
+        <v>0.01</v>
       </c>
       <c r="R434" s="3">
-        <v>9.6080000000000005</v>
+        <v>0.2361</v>
       </c>
       <c r="S434" s="4">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="T434">
-        <v>1086</v>
-      </c>
-      <c r="U434" s="3">
-        <v>0.99270000000000003</v>
-      </c>
-      <c r="V434" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U434" t="s">
+        <v>25</v>
+      </c>
+      <c r="V434" t="s">
+        <v>25</v>
+      </c>
+      <c r="W434">
+        <v>36.558</v>
       </c>
       <c r="X434" t="s">
         <v>41</v>
@@ -31924,7 +31927,7 @@
     </row>
     <row r="435" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B435">
         <v>16</v>
@@ -31945,49 +31948,52 @@
         <v>25</v>
       </c>
       <c r="H435">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I435">
-        <v>15999</v>
+        <v>46702</v>
       </c>
       <c r="J435">
-        <v>121</v>
+        <v>487</v>
       </c>
       <c r="K435">
-        <v>821</v>
+        <v>145</v>
       </c>
       <c r="L435">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="M435">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N435">
         <v>0</v>
       </c>
       <c r="O435" s="2">
-        <v>1.4930555555555556E-3</v>
-      </c>
-      <c r="P435" s="2">
-        <v>3.8194444444444446E-4</v>
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="P435" t="s">
+        <v>24</v>
       </c>
       <c r="Q435" s="3">
-        <v>7.6E-3</v>
+        <v>1.04E-2</v>
       </c>
       <c r="R435" s="3">
-        <v>6.7850000000000001</v>
-      </c>
-      <c r="S435" s="3">
-        <v>1.34E-2</v>
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="S435" s="4">
+        <v>1</v>
       </c>
       <c r="T435">
-        <v>804</v>
-      </c>
-      <c r="U435" s="3">
-        <v>0.99260000000000004</v>
-      </c>
-      <c r="V435" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U435" t="s">
+        <v>25</v>
+      </c>
+      <c r="V435" t="s">
+        <v>25</v>
+      </c>
+      <c r="W435">
+        <v>50.658000000000001</v>
       </c>
       <c r="X435" t="s">
         <v>41</v>
@@ -31995,7 +32001,7 @@
     </row>
     <row r="436" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B436">
         <v>17</v>
@@ -32016,49 +32022,52 @@
         <v>25</v>
       </c>
       <c r="H436">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I436">
-        <v>22246</v>
+        <v>31360</v>
       </c>
       <c r="J436">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="K436">
-        <v>656</v>
+        <v>79</v>
       </c>
       <c r="L436">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="M436">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="N436">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O436" s="2">
-        <v>1.2731481481481483E-3</v>
+        <v>1.3310185185185185E-3</v>
       </c>
       <c r="P436" s="2">
-        <v>1.0995370370370371E-3</v>
+        <v>1.7013888888888888E-3</v>
       </c>
       <c r="Q436" s="3">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="R436" s="4">
-        <v>3.28</v>
-      </c>
-      <c r="S436" s="3">
-        <v>7.4700000000000003E-2</v>
+        <v>8.6E-3</v>
+      </c>
+      <c r="R436" s="3">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="S436" s="4">
+        <v>1</v>
       </c>
       <c r="T436">
-        <v>597</v>
-      </c>
-      <c r="U436" s="3">
-        <v>0.98350000000000004</v>
+        <v>-29</v>
+      </c>
+      <c r="U436" t="s">
+        <v>25</v>
       </c>
       <c r="V436" s="3">
-        <v>1</v>
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="W436">
+        <v>22.295999999999999</v>
       </c>
       <c r="X436" t="s">
         <v>41</v>
@@ -32066,7 +32075,7 @@
     </row>
     <row r="437" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B437">
         <v>18</v>
@@ -32084,16 +32093,16 @@
         <v>43</v>
       </c>
       <c r="G437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H437">
         <v>0</v>
       </c>
       <c r="I437">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="J437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K437">
         <v>0</v>
@@ -32107,17 +32116,17 @@
       <c r="N437">
         <v>0</v>
       </c>
-      <c r="O437" s="2">
-        <v>1.1805555555555556E-3</v>
+      <c r="O437" t="s">
+        <v>24</v>
       </c>
       <c r="P437" t="s">
         <v>24</v>
       </c>
-      <c r="Q437" s="3">
-        <v>9.7000000000000003E-3</v>
-      </c>
-      <c r="R437" s="4">
-        <v>0</v>
+      <c r="Q437" s="4">
+        <v>0</v>
+      </c>
+      <c r="R437" t="s">
+        <v>25</v>
       </c>
       <c r="S437" t="s">
         <v>25</v>
@@ -32128,670 +32137,7 @@
       <c r="U437" t="s">
         <v>25</v>
       </c>
-      <c r="V437" t="s">
-        <v>25</v>
-      </c>
       <c r="X437" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="438" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A438" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B438">
-        <v>10</v>
-      </c>
-      <c r="C438">
-        <v>81</v>
-      </c>
-      <c r="D438">
-        <v>85</v>
-      </c>
-      <c r="E438" t="s">
-        <v>32</v>
-      </c>
-      <c r="F438" t="s">
-        <v>43</v>
-      </c>
-      <c r="G438">
-        <v>25</v>
-      </c>
-      <c r="H438">
-        <v>8</v>
-      </c>
-      <c r="I438">
-        <v>11497</v>
-      </c>
-      <c r="J438">
-        <v>132</v>
-      </c>
-      <c r="K438">
-        <v>52</v>
-      </c>
-      <c r="L438">
-        <v>38</v>
-      </c>
-      <c r="M438">
-        <v>13</v>
-      </c>
-      <c r="N438">
-        <v>0</v>
-      </c>
-      <c r="O438" s="2">
-        <v>9.9537037037037042E-4</v>
-      </c>
-      <c r="P438" s="2">
-        <v>2.3379629629629631E-3</v>
-      </c>
-      <c r="Q438" s="3">
-        <v>1.15E-2</v>
-      </c>
-      <c r="R438" s="3">
-        <v>0.39389999999999997</v>
-      </c>
-      <c r="S438" s="3">
-        <v>0.73080000000000001</v>
-      </c>
-      <c r="T438">
-        <v>1</v>
-      </c>
-      <c r="U438" s="3">
-        <v>7.1400000000000005E-2</v>
-      </c>
-      <c r="V438" s="3">
-        <v>1</v>
-      </c>
-      <c r="W438">
-        <v>3.6659999999999999</v>
-      </c>
-      <c r="X438" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="439" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A439" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B439">
-        <v>11</v>
-      </c>
-      <c r="C439">
-        <v>81</v>
-      </c>
-      <c r="D439">
-        <v>85</v>
-      </c>
-      <c r="E439" t="s">
-        <v>32</v>
-      </c>
-      <c r="F439" t="s">
-        <v>43</v>
-      </c>
-      <c r="G439">
-        <v>25</v>
-      </c>
-      <c r="H439">
-        <v>8</v>
-      </c>
-      <c r="I439">
-        <v>30692</v>
-      </c>
-      <c r="J439">
-        <v>259</v>
-      </c>
-      <c r="K439">
-        <v>89</v>
-      </c>
-      <c r="L439">
-        <v>51</v>
-      </c>
-      <c r="M439">
-        <v>30</v>
-      </c>
-      <c r="N439">
-        <v>2</v>
-      </c>
-      <c r="O439" s="2">
-        <v>1.3541666666666667E-3</v>
-      </c>
-      <c r="P439" s="2">
-        <v>1.8055555555555555E-3</v>
-      </c>
-      <c r="Q439" s="3">
-        <v>8.3999999999999995E-3</v>
-      </c>
-      <c r="R439" s="3">
-        <v>0.34360000000000002</v>
-      </c>
-      <c r="S439" s="3">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="T439">
-        <v>8</v>
-      </c>
-      <c r="U439" s="3">
-        <v>0.21049999999999999</v>
-      </c>
-      <c r="V439" s="3">
-        <v>0.9677</v>
-      </c>
-      <c r="W439">
-        <v>34.128</v>
-      </c>
-      <c r="X439" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="440" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A440" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B440">
-        <v>12</v>
-      </c>
-      <c r="C440">
-        <v>81</v>
-      </c>
-      <c r="D440">
-        <v>85</v>
-      </c>
-      <c r="E440" t="s">
-        <v>32</v>
-      </c>
-      <c r="F440" t="s">
-        <v>43</v>
-      </c>
-      <c r="G440">
-        <v>25</v>
-      </c>
-      <c r="H440">
-        <v>1</v>
-      </c>
-      <c r="I440">
-        <v>33207</v>
-      </c>
-      <c r="J440">
-        <v>240</v>
-      </c>
-      <c r="K440">
-        <v>64</v>
-      </c>
-      <c r="L440">
-        <v>59</v>
-      </c>
-      <c r="M440">
-        <v>1</v>
-      </c>
-      <c r="N440">
-        <v>0</v>
-      </c>
-      <c r="O440" s="2">
-        <v>1.5856481481481481E-3</v>
-      </c>
-      <c r="P440" s="2">
-        <v>2.8935185185185184E-4</v>
-      </c>
-      <c r="Q440" s="3">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="R440" s="3">
-        <v>0.26669999999999999</v>
-      </c>
-      <c r="S440" s="3">
-        <v>0.92190000000000005</v>
-      </c>
-      <c r="T440">
-        <v>4</v>
-      </c>
-      <c r="U440" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="V440" s="3">
-        <v>1</v>
-      </c>
-      <c r="W440">
-        <v>22.643999999999998</v>
-      </c>
-      <c r="X440" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="441" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A441" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B441">
-        <v>13</v>
-      </c>
-      <c r="C441">
-        <v>81</v>
-      </c>
-      <c r="D441">
-        <v>85</v>
-      </c>
-      <c r="E441" t="s">
-        <v>32</v>
-      </c>
-      <c r="F441" t="s">
-        <v>43</v>
-      </c>
-      <c r="G441">
-        <v>44</v>
-      </c>
-      <c r="H441">
-        <v>0</v>
-      </c>
-      <c r="I441">
-        <v>23624</v>
-      </c>
-      <c r="J441">
-        <v>220</v>
-      </c>
-      <c r="K441">
-        <v>40</v>
-      </c>
-      <c r="L441">
-        <v>35</v>
-      </c>
-      <c r="M441">
-        <v>0</v>
-      </c>
-      <c r="N441">
-        <v>0</v>
-      </c>
-      <c r="O441" s="2">
-        <v>1.2268518518518518E-3</v>
-      </c>
-      <c r="P441" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q441" s="3">
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="R441" s="3">
-        <v>0.18179999999999999</v>
-      </c>
-      <c r="S441" s="3">
-        <v>0.875</v>
-      </c>
-      <c r="T441">
-        <v>5</v>
-      </c>
-      <c r="U441" s="4">
-        <v>1</v>
-      </c>
-      <c r="V441" t="s">
-        <v>25</v>
-      </c>
-      <c r="W441">
-        <v>26.43</v>
-      </c>
-      <c r="X441" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="442" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A442" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B442">
-        <v>14</v>
-      </c>
-      <c r="C442">
-        <v>81</v>
-      </c>
-      <c r="D442">
-        <v>85</v>
-      </c>
-      <c r="E442" t="s">
-        <v>32</v>
-      </c>
-      <c r="F442" t="s">
-        <v>43</v>
-      </c>
-      <c r="G442">
-        <v>25</v>
-      </c>
-      <c r="H442">
-        <v>0</v>
-      </c>
-      <c r="I442">
-        <v>22591</v>
-      </c>
-      <c r="J442">
-        <v>239</v>
-      </c>
-      <c r="K442">
-        <v>32</v>
-      </c>
-      <c r="L442">
-        <v>28</v>
-      </c>
-      <c r="M442">
-        <v>0</v>
-      </c>
-      <c r="N442">
-        <v>0</v>
-      </c>
-      <c r="O442" s="2">
-        <v>1.0763888888888889E-3</v>
-      </c>
-      <c r="P442" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q442" s="3">
-        <v>1.06E-2</v>
-      </c>
-      <c r="R442" s="3">
-        <v>0.13389999999999999</v>
-      </c>
-      <c r="S442" s="3">
-        <v>0.875</v>
-      </c>
-      <c r="T442">
-        <v>4</v>
-      </c>
-      <c r="U442" s="4">
-        <v>1</v>
-      </c>
-      <c r="V442" t="s">
-        <v>25</v>
-      </c>
-      <c r="W442">
-        <v>24.654</v>
-      </c>
-      <c r="X442" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="443" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A443" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B443">
-        <v>15</v>
-      </c>
-      <c r="C443">
-        <v>81</v>
-      </c>
-      <c r="D443">
-        <v>85</v>
-      </c>
-      <c r="E443" t="s">
-        <v>32</v>
-      </c>
-      <c r="F443" t="s">
-        <v>43</v>
-      </c>
-      <c r="G443">
-        <v>25</v>
-      </c>
-      <c r="H443">
-        <v>0</v>
-      </c>
-      <c r="I443">
-        <v>21702</v>
-      </c>
-      <c r="J443">
-        <v>216</v>
-      </c>
-      <c r="K443">
-        <v>55</v>
-      </c>
-      <c r="L443">
-        <v>51</v>
-      </c>
-      <c r="M443">
-        <v>0</v>
-      </c>
-      <c r="N443">
-        <v>0</v>
-      </c>
-      <c r="O443" s="2">
-        <v>1.1458333333333333E-3</v>
-      </c>
-      <c r="P443" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q443" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="R443" s="3">
-        <v>0.25459999999999999</v>
-      </c>
-      <c r="S443" s="3">
-        <v>0.92730000000000001</v>
-      </c>
-      <c r="T443">
-        <v>4</v>
-      </c>
-      <c r="U443" s="4">
-        <v>1</v>
-      </c>
-      <c r="V443" t="s">
-        <v>25</v>
-      </c>
-      <c r="W443">
-        <v>36.558</v>
-      </c>
-      <c r="X443" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="444" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A444" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B444">
-        <v>16</v>
-      </c>
-      <c r="C444">
-        <v>81</v>
-      </c>
-      <c r="D444">
-        <v>85</v>
-      </c>
-      <c r="E444" t="s">
-        <v>32</v>
-      </c>
-      <c r="F444" t="s">
-        <v>43</v>
-      </c>
-      <c r="G444">
-        <v>25</v>
-      </c>
-      <c r="H444">
-        <v>0</v>
-      </c>
-      <c r="I444">
-        <v>46702</v>
-      </c>
-      <c r="J444">
-        <v>487</v>
-      </c>
-      <c r="K444">
-        <v>154</v>
-      </c>
-      <c r="L444">
-        <v>145</v>
-      </c>
-      <c r="M444">
-        <v>0</v>
-      </c>
-      <c r="N444">
-        <v>0</v>
-      </c>
-      <c r="O444" s="2">
-        <v>1.0995370370370371E-3</v>
-      </c>
-      <c r="P444" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q444" s="3">
-        <v>1.04E-2</v>
-      </c>
-      <c r="R444" s="3">
-        <v>0.31619999999999998</v>
-      </c>
-      <c r="S444" s="3">
-        <v>0.94159999999999999</v>
-      </c>
-      <c r="T444">
-        <v>9</v>
-      </c>
-      <c r="U444" s="4">
-        <v>1</v>
-      </c>
-      <c r="V444" t="s">
-        <v>25</v>
-      </c>
-      <c r="W444">
-        <v>50.658000000000001</v>
-      </c>
-      <c r="X444" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="445" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A445" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B445">
-        <v>17</v>
-      </c>
-      <c r="C445">
-        <v>81</v>
-      </c>
-      <c r="D445">
-        <v>85</v>
-      </c>
-      <c r="E445" t="s">
-        <v>32</v>
-      </c>
-      <c r="F445" t="s">
-        <v>43</v>
-      </c>
-      <c r="G445">
-        <v>25</v>
-      </c>
-      <c r="H445">
-        <v>5</v>
-      </c>
-      <c r="I445">
-        <v>31360</v>
-      </c>
-      <c r="J445">
-        <v>270</v>
-      </c>
-      <c r="K445">
-        <v>82</v>
-      </c>
-      <c r="L445">
-        <v>38</v>
-      </c>
-      <c r="M445">
-        <v>29</v>
-      </c>
-      <c r="N445">
-        <v>2</v>
-      </c>
-      <c r="O445" s="2">
-        <v>1.3310185185185185E-3</v>
-      </c>
-      <c r="P445" s="2">
-        <v>1.7013888888888888E-3</v>
-      </c>
-      <c r="Q445" s="3">
-        <v>8.6E-3</v>
-      </c>
-      <c r="R445" s="3">
-        <v>0.30370000000000003</v>
-      </c>
-      <c r="S445" s="3">
-        <v>0.46339999999999998</v>
-      </c>
-      <c r="T445">
-        <v>15</v>
-      </c>
-      <c r="U445" s="3">
-        <v>0.34089999999999998</v>
-      </c>
-      <c r="V445" s="3">
-        <v>0.78569999999999995</v>
-      </c>
-      <c r="W445">
-        <v>22.295999999999999</v>
-      </c>
-      <c r="X445" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="446" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A446" s="1">
-        <v>46188</v>
-      </c>
-      <c r="B446">
-        <v>18</v>
-      </c>
-      <c r="C446">
-        <v>81</v>
-      </c>
-      <c r="D446">
-        <v>85</v>
-      </c>
-      <c r="E446" t="s">
-        <v>32</v>
-      </c>
-      <c r="F446" t="s">
-        <v>43</v>
-      </c>
-      <c r="G446">
-        <v>0</v>
-      </c>
-      <c r="H446">
-        <v>0</v>
-      </c>
-      <c r="I446">
-        <v>78</v>
-      </c>
-      <c r="J446">
-        <v>0</v>
-      </c>
-      <c r="K446">
-        <v>0</v>
-      </c>
-      <c r="L446">
-        <v>0</v>
-      </c>
-      <c r="M446">
-        <v>0</v>
-      </c>
-      <c r="N446">
-        <v>0</v>
-      </c>
-      <c r="O446" t="s">
-        <v>24</v>
-      </c>
-      <c r="P446" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q446" s="4">
-        <v>0</v>
-      </c>
-      <c r="R446" t="s">
-        <v>25</v>
-      </c>
-      <c r="S446" t="s">
-        <v>25</v>
-      </c>
-      <c r="T446">
-        <v>0</v>
-      </c>
-      <c r="U446" t="s">
-        <v>25</v>
-      </c>
-      <c r="X446" t="s">
         <v>41</v>
       </c>
     </row>

--- a/data/base_gestor_locator.xlsx
+++ b/data/base_gestor_locator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005B7EB2-DDCC-4781-9330-FD636C68529B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A58EE-1151-41EA-9538-D1EA2DC944C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04AF7731-6CD9-46EC-B877-B9E0C87BB669}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="46">
   <si>
     <t>Data</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Arranha e Ferreira</t>
+  </si>
+  <si>
+    <t>988 - Locator_Bradesco_Comercial</t>
+  </si>
+  <si>
+    <t>RedeBrasil</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAFC8DE-6478-4031-89A9-FB95FCFA4EDA}">
-  <dimension ref="A1:X606"/>
+  <dimension ref="A1:X628"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -44560,6 +44566,1631 @@
         <v>37</v>
       </c>
     </row>
+    <row r="607" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A607" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B607">
+        <v>9</v>
+      </c>
+      <c r="C607">
+        <v>988</v>
+      </c>
+      <c r="D607">
+        <v>990</v>
+      </c>
+      <c r="E607" t="s">
+        <v>44</v>
+      </c>
+      <c r="F607">
+        <v>93609</v>
+      </c>
+      <c r="G607">
+        <v>100</v>
+      </c>
+      <c r="H607">
+        <v>10</v>
+      </c>
+      <c r="I607">
+        <v>34766</v>
+      </c>
+      <c r="J607">
+        <v>1910</v>
+      </c>
+      <c r="K607">
+        <v>68</v>
+      </c>
+      <c r="L607">
+        <v>0</v>
+      </c>
+      <c r="M607">
+        <v>61</v>
+      </c>
+      <c r="N607">
+        <v>2</v>
+      </c>
+      <c r="O607" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P607" s="2">
+        <v>1.9907407407407408E-3</v>
+      </c>
+      <c r="Q607" s="3">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="R607" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="S607" s="4">
+        <v>0</v>
+      </c>
+      <c r="T607">
+        <v>7</v>
+      </c>
+      <c r="U607" s="3">
+        <v>0.10290000000000001</v>
+      </c>
+      <c r="V607" s="3">
+        <v>0.65569999999999995</v>
+      </c>
+      <c r="W607">
+        <v>8.3650000000000002</v>
+      </c>
+      <c r="X607" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="608" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A608" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B608">
+        <v>10</v>
+      </c>
+      <c r="C608">
+        <v>988</v>
+      </c>
+      <c r="D608">
+        <v>990</v>
+      </c>
+      <c r="E608" t="s">
+        <v>44</v>
+      </c>
+      <c r="F608">
+        <v>93609</v>
+      </c>
+      <c r="G608">
+        <v>100</v>
+      </c>
+      <c r="H608">
+        <v>11</v>
+      </c>
+      <c r="I608">
+        <v>65759</v>
+      </c>
+      <c r="J608">
+        <v>3227</v>
+      </c>
+      <c r="K608">
+        <v>95</v>
+      </c>
+      <c r="L608">
+        <v>0</v>
+      </c>
+      <c r="M608">
+        <v>84</v>
+      </c>
+      <c r="N608">
+        <v>3</v>
+      </c>
+      <c r="O608" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P608" s="2">
+        <v>2.4305555555555556E-3</v>
+      </c>
+      <c r="Q608" s="3">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="R608" s="3">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="S608" s="4">
+        <v>0</v>
+      </c>
+      <c r="T608">
+        <v>11</v>
+      </c>
+      <c r="U608" s="3">
+        <v>0.1158</v>
+      </c>
+      <c r="V608" s="3">
+        <v>0.51039999999999996</v>
+      </c>
+      <c r="W608">
+        <v>19.967500000000001</v>
+      </c>
+      <c r="X608" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="609" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A609" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B609">
+        <v>11</v>
+      </c>
+      <c r="C609">
+        <v>988</v>
+      </c>
+      <c r="D609">
+        <v>990</v>
+      </c>
+      <c r="E609" t="s">
+        <v>44</v>
+      </c>
+      <c r="F609">
+        <v>93609</v>
+      </c>
+      <c r="G609">
+        <v>100</v>
+      </c>
+      <c r="H609">
+        <v>11</v>
+      </c>
+      <c r="I609">
+        <v>77495</v>
+      </c>
+      <c r="J609">
+        <v>3903</v>
+      </c>
+      <c r="K609">
+        <v>109</v>
+      </c>
+      <c r="L609">
+        <v>0</v>
+      </c>
+      <c r="M609">
+        <v>103</v>
+      </c>
+      <c r="N609">
+        <v>2</v>
+      </c>
+      <c r="O609" s="2">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P609" s="2">
+        <v>1.4351851851851852E-3</v>
+      </c>
+      <c r="Q609" s="3">
+        <v>5.04E-2</v>
+      </c>
+      <c r="R609" s="3">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="S609" s="4">
+        <v>0</v>
+      </c>
+      <c r="T609">
+        <v>6</v>
+      </c>
+      <c r="U609" s="3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="V609" s="3">
+        <v>0.71679999999999999</v>
+      </c>
+      <c r="W609">
+        <v>26.824000000000002</v>
+      </c>
+      <c r="X609" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="610" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A610" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B610">
+        <v>12</v>
+      </c>
+      <c r="C610">
+        <v>988</v>
+      </c>
+      <c r="D610">
+        <v>990</v>
+      </c>
+      <c r="E610" t="s">
+        <v>44</v>
+      </c>
+      <c r="F610">
+        <v>93609</v>
+      </c>
+      <c r="G610">
+        <v>100</v>
+      </c>
+      <c r="H610">
+        <v>10</v>
+      </c>
+      <c r="I610">
+        <v>82252</v>
+      </c>
+      <c r="J610">
+        <v>3821</v>
+      </c>
+      <c r="K610">
+        <v>106</v>
+      </c>
+      <c r="L610">
+        <v>1</v>
+      </c>
+      <c r="M610">
+        <v>103</v>
+      </c>
+      <c r="N610">
+        <v>1</v>
+      </c>
+      <c r="O610" s="2">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="P610" s="2">
+        <v>1.4004629629629629E-3</v>
+      </c>
+      <c r="Q610" s="3">
+        <v>4.65E-2</v>
+      </c>
+      <c r="R610" s="3">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="S610" s="3">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="T610">
+        <v>2</v>
+      </c>
+      <c r="U610" s="3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="V610" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="W610">
+        <v>20.639500000000002</v>
+      </c>
+      <c r="X610" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="611" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A611" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B611">
+        <v>13</v>
+      </c>
+      <c r="C611">
+        <v>988</v>
+      </c>
+      <c r="D611">
+        <v>990</v>
+      </c>
+      <c r="E611" t="s">
+        <v>44</v>
+      </c>
+      <c r="F611">
+        <v>93609</v>
+      </c>
+      <c r="G611">
+        <v>100</v>
+      </c>
+      <c r="H611">
+        <v>5</v>
+      </c>
+      <c r="I611">
+        <v>32584</v>
+      </c>
+      <c r="J611">
+        <v>2012</v>
+      </c>
+      <c r="K611">
+        <v>36</v>
+      </c>
+      <c r="L611">
+        <v>1</v>
+      </c>
+      <c r="M611">
+        <v>28</v>
+      </c>
+      <c r="N611">
+        <v>0</v>
+      </c>
+      <c r="O611" s="2">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P611" s="2">
+        <v>1.4814814814814814E-3</v>
+      </c>
+      <c r="Q611" s="3">
+        <v>6.1699999999999998E-2</v>
+      </c>
+      <c r="R611" s="3">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="S611" s="3">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="T611">
+        <v>7</v>
+      </c>
+      <c r="U611" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V611" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="W611">
+        <v>21.35</v>
+      </c>
+      <c r="X611" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="612" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A612" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B612">
+        <v>14</v>
+      </c>
+      <c r="C612">
+        <v>988</v>
+      </c>
+      <c r="D612">
+        <v>990</v>
+      </c>
+      <c r="E612" t="s">
+        <v>44</v>
+      </c>
+      <c r="F612">
+        <v>93609</v>
+      </c>
+      <c r="G612">
+        <v>100</v>
+      </c>
+      <c r="H612">
+        <v>10</v>
+      </c>
+      <c r="I612">
+        <v>44827</v>
+      </c>
+      <c r="J612">
+        <v>2872</v>
+      </c>
+      <c r="K612">
+        <v>72</v>
+      </c>
+      <c r="L612">
+        <v>0</v>
+      </c>
+      <c r="M612">
+        <v>72</v>
+      </c>
+      <c r="N612">
+        <v>1</v>
+      </c>
+      <c r="O612" s="2">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P612" s="2">
+        <v>1.238425925925926E-3</v>
+      </c>
+      <c r="Q612" s="3">
+        <v>6.4100000000000004E-2</v>
+      </c>
+      <c r="R612" s="3">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="S612" s="4">
+        <v>0</v>
+      </c>
+      <c r="T612">
+        <v>0</v>
+      </c>
+      <c r="U612" s="4">
+        <v>0</v>
+      </c>
+      <c r="V612" s="3">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="W612">
+        <v>18.791499999999999</v>
+      </c>
+      <c r="X612" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="613" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A613" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B613">
+        <v>15</v>
+      </c>
+      <c r="C613">
+        <v>988</v>
+      </c>
+      <c r="D613">
+        <v>990</v>
+      </c>
+      <c r="E613" t="s">
+        <v>44</v>
+      </c>
+      <c r="F613">
+        <v>93609</v>
+      </c>
+      <c r="G613">
+        <v>100</v>
+      </c>
+      <c r="H613">
+        <v>17</v>
+      </c>
+      <c r="I613">
+        <v>85556</v>
+      </c>
+      <c r="J613">
+        <v>4015</v>
+      </c>
+      <c r="K613">
+        <v>110</v>
+      </c>
+      <c r="L613">
+        <v>3</v>
+      </c>
+      <c r="M613">
+        <v>107</v>
+      </c>
+      <c r="N613">
+        <v>5</v>
+      </c>
+      <c r="O613" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P613" s="2">
+        <v>1.6087962962962963E-3</v>
+      </c>
+      <c r="Q613" s="3">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="R613" s="3">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="S613" s="3">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="T613">
+        <v>0</v>
+      </c>
+      <c r="U613" s="4">
+        <v>0</v>
+      </c>
+      <c r="V613" s="3">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="W613">
+        <v>17.913</v>
+      </c>
+      <c r="X613" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="614" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A614" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B614">
+        <v>16</v>
+      </c>
+      <c r="C614">
+        <v>988</v>
+      </c>
+      <c r="D614">
+        <v>990</v>
+      </c>
+      <c r="E614" t="s">
+        <v>44</v>
+      </c>
+      <c r="F614">
+        <v>93609</v>
+      </c>
+      <c r="G614">
+        <v>100</v>
+      </c>
+      <c r="H614">
+        <v>10</v>
+      </c>
+      <c r="I614">
+        <v>71109</v>
+      </c>
+      <c r="J614">
+        <v>3318</v>
+      </c>
+      <c r="K614">
+        <v>80</v>
+      </c>
+      <c r="L614">
+        <v>2</v>
+      </c>
+      <c r="M614">
+        <v>78</v>
+      </c>
+      <c r="N614">
+        <v>1</v>
+      </c>
+      <c r="O614" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P614" s="2">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q614" s="3">
+        <v>4.6699999999999998E-2</v>
+      </c>
+      <c r="R614" s="3">
+        <v>2.41E-2</v>
+      </c>
+      <c r="S614" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T614">
+        <v>0</v>
+      </c>
+      <c r="U614" s="4">
+        <v>0</v>
+      </c>
+      <c r="V614" s="3">
+        <v>0.98719999999999997</v>
+      </c>
+      <c r="W614">
+        <v>16.131499999999999</v>
+      </c>
+      <c r="X614" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="615" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A615" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B615">
+        <v>17</v>
+      </c>
+      <c r="C615">
+        <v>988</v>
+      </c>
+      <c r="D615">
+        <v>990</v>
+      </c>
+      <c r="E615" t="s">
+        <v>44</v>
+      </c>
+      <c r="F615">
+        <v>93609</v>
+      </c>
+      <c r="G615">
+        <v>100</v>
+      </c>
+      <c r="H615">
+        <v>10</v>
+      </c>
+      <c r="I615">
+        <v>38685</v>
+      </c>
+      <c r="J615">
+        <v>2157</v>
+      </c>
+      <c r="K615">
+        <v>47</v>
+      </c>
+      <c r="L615">
+        <v>1</v>
+      </c>
+      <c r="M615">
+        <v>33</v>
+      </c>
+      <c r="N615">
+        <v>1</v>
+      </c>
+      <c r="O615" s="2">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P615" s="2">
+        <v>1.9791666666666668E-3</v>
+      </c>
+      <c r="Q615" s="3">
+        <v>5.5800000000000002E-2</v>
+      </c>
+      <c r="R615" s="3">
+        <v>2.18E-2</v>
+      </c>
+      <c r="S615" s="3">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="T615">
+        <v>13</v>
+      </c>
+      <c r="U615" s="3">
+        <v>0.28260000000000002</v>
+      </c>
+      <c r="V615" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="W615">
+        <v>15.900499999999999</v>
+      </c>
+      <c r="X615" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="616" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A616" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B616">
+        <v>18</v>
+      </c>
+      <c r="C616">
+        <v>988</v>
+      </c>
+      <c r="D616">
+        <v>990</v>
+      </c>
+      <c r="E616" t="s">
+        <v>44</v>
+      </c>
+      <c r="F616">
+        <v>93609</v>
+      </c>
+      <c r="G616">
+        <v>10</v>
+      </c>
+      <c r="H616">
+        <v>0</v>
+      </c>
+      <c r="I616">
+        <v>144</v>
+      </c>
+      <c r="J616">
+        <v>10</v>
+      </c>
+      <c r="K616">
+        <v>0</v>
+      </c>
+      <c r="L616">
+        <v>0</v>
+      </c>
+      <c r="M616">
+        <v>0</v>
+      </c>
+      <c r="N616">
+        <v>0</v>
+      </c>
+      <c r="O616" s="2">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P616" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q616" s="3">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="R616" s="4">
+        <v>0</v>
+      </c>
+      <c r="S616" t="s">
+        <v>25</v>
+      </c>
+      <c r="T616">
+        <v>0</v>
+      </c>
+      <c r="U616" t="s">
+        <v>25</v>
+      </c>
+      <c r="W616">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="X616" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="617" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A617" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B617">
+        <v>14</v>
+      </c>
+      <c r="C617">
+        <v>988</v>
+      </c>
+      <c r="D617">
+        <v>990</v>
+      </c>
+      <c r="E617" t="s">
+        <v>44</v>
+      </c>
+      <c r="F617">
+        <v>92589</v>
+      </c>
+      <c r="G617">
+        <v>100</v>
+      </c>
+      <c r="H617">
+        <v>12</v>
+      </c>
+      <c r="I617">
+        <v>59450</v>
+      </c>
+      <c r="J617">
+        <v>2934</v>
+      </c>
+      <c r="K617">
+        <v>80</v>
+      </c>
+      <c r="L617">
+        <v>3</v>
+      </c>
+      <c r="M617">
+        <v>77</v>
+      </c>
+      <c r="N617">
+        <v>2</v>
+      </c>
+      <c r="O617" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P617" s="2">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="Q617" s="3">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="R617" s="3">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="S617" s="3">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="T617">
+        <v>0</v>
+      </c>
+      <c r="U617" s="4">
+        <v>0</v>
+      </c>
+      <c r="V617" s="3">
+        <v>0.90910000000000002</v>
+      </c>
+      <c r="W617">
+        <v>36.826999999999998</v>
+      </c>
+      <c r="X617" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="618" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A618" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B618">
+        <v>15</v>
+      </c>
+      <c r="C618">
+        <v>988</v>
+      </c>
+      <c r="D618">
+        <v>990</v>
+      </c>
+      <c r="E618" t="s">
+        <v>44</v>
+      </c>
+      <c r="F618">
+        <v>92589</v>
+      </c>
+      <c r="G618">
+        <v>100</v>
+      </c>
+      <c r="H618">
+        <v>10</v>
+      </c>
+      <c r="I618">
+        <v>22563</v>
+      </c>
+      <c r="J618">
+        <v>953</v>
+      </c>
+      <c r="K618">
+        <v>14</v>
+      </c>
+      <c r="L618">
+        <v>0</v>
+      </c>
+      <c r="M618">
+        <v>14</v>
+      </c>
+      <c r="N618">
+        <v>1</v>
+      </c>
+      <c r="O618" s="2">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P618" s="2">
+        <v>2.5925925925925925E-3</v>
+      </c>
+      <c r="Q618" s="3">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="R618" s="3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="S618" s="4">
+        <v>0</v>
+      </c>
+      <c r="T618">
+        <v>0</v>
+      </c>
+      <c r="U618" s="4">
+        <v>0</v>
+      </c>
+      <c r="V618" s="3">
+        <v>1</v>
+      </c>
+      <c r="W618">
+        <v>12.4495</v>
+      </c>
+      <c r="X618" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="619" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A619" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B619">
+        <v>16</v>
+      </c>
+      <c r="C619">
+        <v>988</v>
+      </c>
+      <c r="D619">
+        <v>990</v>
+      </c>
+      <c r="E619" t="s">
+        <v>44</v>
+      </c>
+      <c r="F619">
+        <v>92589</v>
+      </c>
+      <c r="G619">
+        <v>100</v>
+      </c>
+      <c r="H619">
+        <v>4</v>
+      </c>
+      <c r="I619">
+        <v>14152</v>
+      </c>
+      <c r="J619">
+        <v>683</v>
+      </c>
+      <c r="K619">
+        <v>8</v>
+      </c>
+      <c r="L619">
+        <v>0</v>
+      </c>
+      <c r="M619">
+        <v>8</v>
+      </c>
+      <c r="N619">
+        <v>1</v>
+      </c>
+      <c r="O619" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P619" s="2">
+        <v>3.8310185185185183E-3</v>
+      </c>
+      <c r="Q619" s="3">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="R619" s="3">
+        <v>1.17E-2</v>
+      </c>
+      <c r="S619" s="4">
+        <v>0</v>
+      </c>
+      <c r="T619">
+        <v>0</v>
+      </c>
+      <c r="U619" s="4">
+        <v>0</v>
+      </c>
+      <c r="V619" s="3">
+        <v>1</v>
+      </c>
+      <c r="W619">
+        <v>10.976000000000001</v>
+      </c>
+      <c r="X619" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="620" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A620" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B620">
+        <v>15</v>
+      </c>
+      <c r="C620">
+        <v>988</v>
+      </c>
+      <c r="D620">
+        <v>990</v>
+      </c>
+      <c r="E620" t="s">
+        <v>44</v>
+      </c>
+      <c r="F620">
+        <v>92414</v>
+      </c>
+      <c r="G620">
+        <v>200</v>
+      </c>
+      <c r="H620">
+        <v>0</v>
+      </c>
+      <c r="I620">
+        <v>74502</v>
+      </c>
+      <c r="J620">
+        <v>3914</v>
+      </c>
+      <c r="K620">
+        <v>69</v>
+      </c>
+      <c r="L620">
+        <v>69</v>
+      </c>
+      <c r="M620">
+        <v>0</v>
+      </c>
+      <c r="N620">
+        <v>0</v>
+      </c>
+      <c r="O620" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="P620" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q620" s="3">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="R620" s="3">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="S620" s="4">
+        <v>1</v>
+      </c>
+      <c r="T620">
+        <v>0</v>
+      </c>
+      <c r="U620" t="s">
+        <v>25</v>
+      </c>
+      <c r="V620" s="3">
+        <v>0.77049999999999996</v>
+      </c>
+      <c r="W620">
+        <v>60.865000000000002</v>
+      </c>
+      <c r="X620" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="621" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A621" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B621">
+        <v>16</v>
+      </c>
+      <c r="C621">
+        <v>988</v>
+      </c>
+      <c r="D621">
+        <v>990</v>
+      </c>
+      <c r="E621" t="s">
+        <v>44</v>
+      </c>
+      <c r="F621">
+        <v>92414</v>
+      </c>
+      <c r="G621">
+        <v>405</v>
+      </c>
+      <c r="H621">
+        <v>0</v>
+      </c>
+      <c r="I621">
+        <v>192083</v>
+      </c>
+      <c r="J621">
+        <v>9340</v>
+      </c>
+      <c r="K621">
+        <v>190</v>
+      </c>
+      <c r="L621">
+        <v>190</v>
+      </c>
+      <c r="M621">
+        <v>0</v>
+      </c>
+      <c r="N621">
+        <v>0</v>
+      </c>
+      <c r="O621" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P621" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q621" s="3">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="R621" s="3">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="S621" s="4">
+        <v>1</v>
+      </c>
+      <c r="T621">
+        <v>0</v>
+      </c>
+      <c r="U621" t="s">
+        <v>25</v>
+      </c>
+      <c r="V621" s="3">
+        <v>0.86260000000000003</v>
+      </c>
+      <c r="W621">
+        <v>136.43</v>
+      </c>
+      <c r="X621" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="622" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A622" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B622">
+        <v>17</v>
+      </c>
+      <c r="C622">
+        <v>988</v>
+      </c>
+      <c r="D622">
+        <v>990</v>
+      </c>
+      <c r="E622" t="s">
+        <v>44</v>
+      </c>
+      <c r="F622">
+        <v>92414</v>
+      </c>
+      <c r="G622">
+        <v>400</v>
+      </c>
+      <c r="H622">
+        <v>0</v>
+      </c>
+      <c r="I622">
+        <v>55033</v>
+      </c>
+      <c r="J622">
+        <v>2746</v>
+      </c>
+      <c r="K622">
+        <v>62</v>
+      </c>
+      <c r="L622">
+        <v>62</v>
+      </c>
+      <c r="M622">
+        <v>0</v>
+      </c>
+      <c r="N622">
+        <v>0</v>
+      </c>
+      <c r="O622" s="2">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="P622" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q622" s="3">
+        <v>4.99E-2</v>
+      </c>
+      <c r="R622" s="3">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="S622" s="4">
+        <v>1</v>
+      </c>
+      <c r="T622">
+        <v>0</v>
+      </c>
+      <c r="U622" t="s">
+        <v>25</v>
+      </c>
+      <c r="V622" s="3">
+        <v>0.82140000000000002</v>
+      </c>
+      <c r="W622">
+        <v>33.131</v>
+      </c>
+      <c r="X622" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="623" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A623" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B623">
+        <v>9</v>
+      </c>
+      <c r="C623">
+        <v>988</v>
+      </c>
+      <c r="D623">
+        <v>990</v>
+      </c>
+      <c r="E623" t="s">
+        <v>44</v>
+      </c>
+      <c r="F623">
+        <v>79244</v>
+      </c>
+      <c r="G623">
+        <v>400</v>
+      </c>
+      <c r="H623">
+        <v>15</v>
+      </c>
+      <c r="I623">
+        <v>84895</v>
+      </c>
+      <c r="J623">
+        <v>4768</v>
+      </c>
+      <c r="K623">
+        <v>138</v>
+      </c>
+      <c r="L623">
+        <v>2</v>
+      </c>
+      <c r="M623">
+        <v>125</v>
+      </c>
+      <c r="N623">
+        <v>5</v>
+      </c>
+      <c r="O623" s="2">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="P623" s="2">
+        <v>1.7013888888888888E-3</v>
+      </c>
+      <c r="Q623" s="3">
+        <v>5.62E-2</v>
+      </c>
+      <c r="R623" s="3">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="S623" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="T623">
+        <v>11</v>
+      </c>
+      <c r="U623" s="3">
+        <v>8.09E-2</v>
+      </c>
+      <c r="V623" s="3">
+        <v>0.748</v>
+      </c>
+      <c r="W623">
+        <v>129.1815</v>
+      </c>
+      <c r="X623" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="624" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A624" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B624">
+        <v>10</v>
+      </c>
+      <c r="C624">
+        <v>988</v>
+      </c>
+      <c r="D624">
+        <v>990</v>
+      </c>
+      <c r="E624" t="s">
+        <v>44</v>
+      </c>
+      <c r="F624">
+        <v>79244</v>
+      </c>
+      <c r="G624">
+        <v>400</v>
+      </c>
+      <c r="H624">
+        <v>19</v>
+      </c>
+      <c r="I624">
+        <v>138015</v>
+      </c>
+      <c r="J624">
+        <v>6663</v>
+      </c>
+      <c r="K624">
+        <v>212</v>
+      </c>
+      <c r="L624">
+        <v>5</v>
+      </c>
+      <c r="M624">
+        <v>197</v>
+      </c>
+      <c r="N624">
+        <v>8</v>
+      </c>
+      <c r="O624" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P624" s="2">
+        <v>1.7939814814814815E-3</v>
+      </c>
+      <c r="Q624" s="3">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="R624" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="S624" s="3">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="T624">
+        <v>10</v>
+      </c>
+      <c r="U624" s="3">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="V624" s="3">
+        <v>0.76259999999999994</v>
+      </c>
+      <c r="W624">
+        <v>117.306</v>
+      </c>
+      <c r="X624" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="625" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A625" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B625">
+        <v>11</v>
+      </c>
+      <c r="C625">
+        <v>988</v>
+      </c>
+      <c r="D625">
+        <v>990</v>
+      </c>
+      <c r="E625" t="s">
+        <v>44</v>
+      </c>
+      <c r="F625">
+        <v>79244</v>
+      </c>
+      <c r="G625">
+        <v>400</v>
+      </c>
+      <c r="H625">
+        <v>19</v>
+      </c>
+      <c r="I625">
+        <v>138472</v>
+      </c>
+      <c r="J625">
+        <v>8281</v>
+      </c>
+      <c r="K625">
+        <v>207</v>
+      </c>
+      <c r="L625">
+        <v>4</v>
+      </c>
+      <c r="M625">
+        <v>193</v>
+      </c>
+      <c r="N625">
+        <v>4</v>
+      </c>
+      <c r="O625" s="2">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P625" s="2">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="Q625" s="3">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="R625" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S625" s="3">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="T625">
+        <v>10</v>
+      </c>
+      <c r="U625" s="3">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="V625" s="3">
+        <v>0.81579999999999997</v>
+      </c>
+      <c r="W625">
+        <v>137.578</v>
+      </c>
+      <c r="X625" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="626" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A626" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B626">
+        <v>12</v>
+      </c>
+      <c r="C626">
+        <v>988</v>
+      </c>
+      <c r="D626">
+        <v>990</v>
+      </c>
+      <c r="E626" t="s">
+        <v>44</v>
+      </c>
+      <c r="F626">
+        <v>79244</v>
+      </c>
+      <c r="G626">
+        <v>400</v>
+      </c>
+      <c r="H626">
+        <v>15</v>
+      </c>
+      <c r="I626">
+        <v>120655</v>
+      </c>
+      <c r="J626">
+        <v>5189</v>
+      </c>
+      <c r="K626">
+        <v>164</v>
+      </c>
+      <c r="L626">
+        <v>4</v>
+      </c>
+      <c r="M626">
+        <v>155</v>
+      </c>
+      <c r="N626">
+        <v>4</v>
+      </c>
+      <c r="O626" s="2">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="P626" s="2">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q626" s="3">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="R626" s="3">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="S626" s="3">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="T626">
+        <v>5</v>
+      </c>
+      <c r="U626" s="3">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="V626" s="3">
+        <v>0.82140000000000002</v>
+      </c>
+      <c r="W626">
+        <v>75.750500000000002</v>
+      </c>
+      <c r="X626" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="627" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A627" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B627">
+        <v>13</v>
+      </c>
+      <c r="C627">
+        <v>988</v>
+      </c>
+      <c r="D627">
+        <v>990</v>
+      </c>
+      <c r="E627" t="s">
+        <v>44</v>
+      </c>
+      <c r="F627">
+        <v>79244</v>
+      </c>
+      <c r="G627">
+        <v>400</v>
+      </c>
+      <c r="H627">
+        <v>13</v>
+      </c>
+      <c r="I627">
+        <v>103171</v>
+      </c>
+      <c r="J627">
+        <v>4202</v>
+      </c>
+      <c r="K627">
+        <v>112</v>
+      </c>
+      <c r="L627">
+        <v>1</v>
+      </c>
+      <c r="M627">
+        <v>88</v>
+      </c>
+      <c r="N627">
+        <v>3</v>
+      </c>
+      <c r="O627" s="2">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="P627" s="2">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="Q627" s="3">
+        <v>4.07E-2</v>
+      </c>
+      <c r="R627" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="S627" s="3">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="T627">
+        <v>23</v>
+      </c>
+      <c r="U627" s="3">
+        <v>0.2072</v>
+      </c>
+      <c r="V627" s="3">
+        <v>0.70209999999999995</v>
+      </c>
+      <c r="W627">
+        <v>64.105999999999995</v>
+      </c>
+      <c r="X627" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="628" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B628">
+        <v>14</v>
+      </c>
+      <c r="C628">
+        <v>988</v>
+      </c>
+      <c r="D628">
+        <v>990</v>
+      </c>
+      <c r="E628" t="s">
+        <v>44</v>
+      </c>
+      <c r="F628">
+        <v>79244</v>
+      </c>
+      <c r="G628">
+        <v>400</v>
+      </c>
+      <c r="H628">
+        <v>29</v>
+      </c>
+      <c r="I628">
+        <v>183672</v>
+      </c>
+      <c r="J628">
+        <v>8883</v>
+      </c>
+      <c r="K628">
+        <v>263</v>
+      </c>
+      <c r="L628">
+        <v>27</v>
+      </c>
+      <c r="M628">
+        <v>232</v>
+      </c>
+      <c r="N628">
+        <v>5</v>
+      </c>
+      <c r="O628" s="2">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="P628" s="2">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="Q628" s="3">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="R628" s="3">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="S628" s="3">
+        <v>0.1027</v>
+      </c>
+      <c r="T628">
+        <v>4</v>
+      </c>
+      <c r="U628" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="V628" s="3">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="W628">
+        <v>179.18600000000001</v>
+      </c>
+      <c r="X628" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
